--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Short Term Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Short Term Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="295">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Short Term Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,7 +76,28 @@
     <t>IN0020210137</t>
   </si>
   <si>
-    <t>IN0020230010</t>
+    <t>IN0020240126</t>
+  </si>
+  <si>
+    <t>IN0020210020</t>
+  </si>
+  <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>State Government of Chhattisgarh</t>
+  </si>
+  <si>
+    <t>IN3520240083</t>
   </si>
   <si>
     <t>IN0020230036</t>
@@ -85,31 +106,43 @@
     <t>IN0020240076</t>
   </si>
   <si>
-    <t>IN0020240126</t>
-  </si>
-  <si>
-    <t>IN0020230085</t>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
+  </si>
+  <si>
+    <t>State Government of Rajasthan</t>
+  </si>
+  <si>
+    <t>IN2920170122</t>
+  </si>
+  <si>
+    <t>State Government of Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>IN3320170126</t>
+  </si>
+  <si>
+    <t>IN0020230119</t>
+  </si>
+  <si>
+    <t>IN2920160214</t>
   </si>
   <si>
     <t>IN0020220151</t>
   </si>
   <si>
-    <t>State Government of Rajasthan</t>
-  </si>
-  <si>
-    <t>IN2920170122</t>
-  </si>
-  <si>
-    <t>State Government of Uttar Pradesh</t>
-  </si>
-  <si>
-    <t>IN3320170126</t>
-  </si>
-  <si>
-    <t>IN0020230119</t>
-  </si>
-  <si>
-    <t>IN2920160214</t>
+    <t>^</t>
+  </si>
+  <si>
+    <t>IN0020240134</t>
   </si>
   <si>
     <t>State Government of Andhra Pradesh</t>
@@ -118,438 +151,465 @@
     <t>IN1020160405</t>
   </si>
   <si>
-    <t>^</t>
-  </si>
-  <si>
     <t>IN2920160156</t>
   </si>
   <si>
-    <t>IN0020240134</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A07RF8</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
     <t>NABARD</t>
   </si>
   <si>
     <t>INE261F08DX0</t>
   </si>
   <si>
-    <t>CRISIL AAA</t>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F08EM1</t>
+  </si>
+  <si>
+    <t>ICRA AAA</t>
+  </si>
+  <si>
+    <t>Small Industries Development Bank Of India. **</t>
+  </si>
+  <si>
+    <t>INE556F08KJ7</t>
+  </si>
+  <si>
+    <t>INE556F08KH1</t>
+  </si>
+  <si>
+    <t>INE261F08EA6</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E08NL6</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE414G07IQ8</t>
+  </si>
+  <si>
+    <t>CRISIL AA+</t>
+  </si>
+  <si>
+    <t>Summit Digitel Infrastructure Private Ltd. **</t>
+  </si>
+  <si>
+    <t>INE507T07146</t>
+  </si>
+  <si>
+    <t>INE556F08KT6</t>
+  </si>
+  <si>
+    <t>Pipeline Infrastructure Pvt Ltd. **</t>
+  </si>
+  <si>
+    <t>INE01XX07034</t>
+  </si>
+  <si>
+    <t>TVS Holdings Ltd. **</t>
+  </si>
+  <si>
+    <t>INE105A08030</t>
+  </si>
+  <si>
+    <t>CARE AA+</t>
+  </si>
+  <si>
+    <t>INE414G07JL7</t>
+  </si>
+  <si>
+    <t>INE115A07QW5</t>
+  </si>
+  <si>
+    <t>INE134E08NP7</t>
+  </si>
+  <si>
+    <t>Bharti Telecom Ltd. **</t>
+  </si>
+  <si>
+    <t>INE403D08207</t>
+  </si>
+  <si>
+    <t>DLF Cyber City Developers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE186K07098</t>
+  </si>
+  <si>
+    <t>ICRA AA+</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd. **</t>
+  </si>
+  <si>
+    <t>INE093I07074</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE134E08MT1</t>
+  </si>
+  <si>
+    <t>Nexus Select Trust **</t>
+  </si>
+  <si>
+    <t>INE0NDH07050</t>
+  </si>
+  <si>
+    <t>Tata Capital Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE033L07IN3</t>
+  </si>
+  <si>
+    <t>EMBASSY OFFICE PARKS REIT **</t>
+  </si>
+  <si>
+    <t>INE041007092</t>
+  </si>
+  <si>
+    <t>Avanse Financial Services Ltd **</t>
+  </si>
+  <si>
+    <t>INE087P07410</t>
+  </si>
+  <si>
+    <t>CRISIL AA-</t>
+  </si>
+  <si>
+    <t>INE041007134</t>
+  </si>
+  <si>
+    <t>INE041007126</t>
+  </si>
+  <si>
+    <t>INE556F08KU4</t>
+  </si>
+  <si>
+    <t>INE134E08LZ0</t>
+  </si>
+  <si>
+    <t>INE261F08EI9</t>
   </si>
   <si>
     <t>Small Industries Development Bank Of India.</t>
   </si>
   <si>
-    <t>INE556F08KJ7</t>
-  </si>
-  <si>
-    <t>INE556F08KH1</t>
-  </si>
-  <si>
-    <t>INE261F08EA6</t>
-  </si>
-  <si>
-    <t>INE261F08EM1</t>
-  </si>
-  <si>
-    <t>ICRA AAA</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G07IQ8</t>
-  </si>
-  <si>
-    <t>CRISIL AA+</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE115A07QE3</t>
-  </si>
-  <si>
-    <t>Small Industries Development Bank Of India. **</t>
-  </si>
-  <si>
-    <t>INE556F08KD0</t>
-  </si>
-  <si>
-    <t>Summit Digitel Infrastructure Private Ltd. **</t>
-  </si>
-  <si>
-    <t>INE507T07146</t>
-  </si>
-  <si>
-    <t>Pipeline Infrastructure Pvt Ltd. **</t>
-  </si>
-  <si>
-    <t>INE01XX07034</t>
-  </si>
-  <si>
-    <t>TVS Holdings Ltd. **</t>
-  </si>
-  <si>
-    <t>INE105A08030</t>
-  </si>
-  <si>
-    <t>CARE AA+</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE414G07JL7</t>
-  </si>
-  <si>
-    <t>Bharti Telecom Ltd. **</t>
-  </si>
-  <si>
-    <t>INE403D08207</t>
-  </si>
-  <si>
-    <t>DLF Cyber City Developers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE186K07098</t>
-  </si>
-  <si>
-    <t>ICRA AA+</t>
-  </si>
-  <si>
-    <t>EMBASSY OFFICE PARKS REIT **</t>
-  </si>
-  <si>
-    <t>INE041007134</t>
-  </si>
-  <si>
-    <t>INE041007126</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE134E08MT1</t>
-  </si>
-  <si>
-    <t>Avanse Financial Services Ltd **</t>
-  </si>
-  <si>
-    <t>INE087P07410</t>
-  </si>
-  <si>
-    <t>CRISIL AA-</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd. **</t>
-  </si>
-  <si>
-    <t>INE093I07074</t>
-  </si>
-  <si>
-    <t>INE041007092</t>
-  </si>
-  <si>
-    <t>INE134E08LZ0</t>
-  </si>
-  <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F08DW2</t>
+    <t>INE556F08KS8</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd. **</t>
+  </si>
+  <si>
+    <t>INE813H07333</t>
+  </si>
+  <si>
+    <t>Sundaram Home Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE667F07IU5</t>
+  </si>
+  <si>
+    <t>Citicorp Finance (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE915D08CY6</t>
+  </si>
+  <si>
+    <t>TVS Credit Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE729N08048</t>
+  </si>
+  <si>
+    <t>Cholamandalam Investment And Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE121A08PT9</t>
+  </si>
+  <si>
+    <t>INE261F08EF5</t>
+  </si>
+  <si>
+    <t>Nirma Ltd. **</t>
+  </si>
+  <si>
+    <t>INE091A07208</t>
+  </si>
+  <si>
+    <t>CRISIL AA</t>
+  </si>
+  <si>
+    <t>INE556F08KI9</t>
+  </si>
+  <si>
+    <t>SMFG India Home Finance Company Ltd **</t>
+  </si>
+  <si>
+    <t>INE213W07319</t>
+  </si>
+  <si>
+    <t>CARE AAA</t>
+  </si>
+  <si>
+    <t>360 One Prime Ltd.</t>
+  </si>
+  <si>
+    <t>INE248U07EQ0</t>
+  </si>
+  <si>
+    <t>INE033L07HZ9</t>
+  </si>
+  <si>
+    <t>INE729N08089</t>
+  </si>
+  <si>
+    <t>INE556F08KK5</t>
+  </si>
+  <si>
+    <t>INE115A07QY1</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd. **</t>
+  </si>
+  <si>
+    <t>INE775A08089</t>
+  </si>
+  <si>
+    <t>FITCH AAA</t>
   </si>
   <si>
     <t>INE403D08157</t>
   </si>
   <si>
-    <t>INE261F08DT8</t>
-  </si>
-  <si>
-    <t>INE261F08DO9</t>
-  </si>
-  <si>
-    <t>Torrent Power Ltd. **</t>
-  </si>
-  <si>
-    <t>INE813H07333</t>
-  </si>
-  <si>
-    <t>Sundaram Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE667F07IU5</t>
-  </si>
-  <si>
-    <t>INE556F08KT6</t>
-  </si>
-  <si>
-    <t>Citicorp Finance (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE915D08CY6</t>
-  </si>
-  <si>
-    <t>TVS Credit Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE729N08048</t>
-  </si>
-  <si>
-    <t>CRISIL AA</t>
-  </si>
-  <si>
-    <t>Nirma Ltd. **</t>
-  </si>
-  <si>
-    <t>INE091A07208</t>
-  </si>
-  <si>
-    <t>INE556F08KI9</t>
+    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE128M08078</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(CE)</t>
+  </si>
+  <si>
+    <t>INE556F08KL3</t>
+  </si>
+  <si>
+    <t>INE115A07RB7</t>
+  </si>
+  <si>
+    <t>INE775A08097</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE233A08121</t>
+  </si>
+  <si>
+    <t>Narayana Hrudayalaya Ltd. **</t>
+  </si>
+  <si>
+    <t>INE410P08016</t>
+  </si>
+  <si>
+    <t>ICRA AA</t>
+  </si>
+  <si>
+    <t>Tata Projects Ltd. **</t>
+  </si>
+  <si>
+    <t>INE725H08246</t>
+  </si>
+  <si>
+    <t>FITCH AA</t>
+  </si>
+  <si>
+    <t>ICICI Home Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE071G07843</t>
+  </si>
+  <si>
+    <t>TMF Holdings Ltd. **</t>
+  </si>
+  <si>
+    <t>INE909H08311</t>
+  </si>
+  <si>
+    <t>INE071G07777</t>
+  </si>
+  <si>
+    <t>Altius Telecom Infrastructure Trust. **</t>
+  </si>
+  <si>
+    <t>INE0BWS08019</t>
+  </si>
+  <si>
+    <t>SMFG India Credit Company Ltd **</t>
+  </si>
+  <si>
+    <t>INE535H07CK4</t>
+  </si>
+  <si>
+    <t>INE115A07MQ6</t>
+  </si>
+  <si>
+    <t>INE915D08CX8</t>
+  </si>
+  <si>
+    <t>INE507T07096</t>
+  </si>
+  <si>
+    <t>INE261F08DV4</t>
+  </si>
+  <si>
+    <t>INE115A07JW0</t>
+  </si>
+  <si>
+    <t>SMFG India Home Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE213W07293</t>
+  </si>
+  <si>
+    <t>INE041007167</t>
+  </si>
+  <si>
+    <t>Summit Digitel Infrastructure Ltd **</t>
+  </si>
+  <si>
+    <t>INE507T07062</t>
+  </si>
+  <si>
+    <t>INE115A07PV9</t>
+  </si>
+  <si>
+    <t>INE115A07NU6</t>
+  </si>
+  <si>
+    <t>Eris Lifesciences Ltd. **</t>
+  </si>
+  <si>
+    <t>INE406M08011</t>
+  </si>
+  <si>
+    <t>INE556F08KM1</t>
+  </si>
+  <si>
+    <t>INE406M08029</t>
+  </si>
+  <si>
+    <t>INE041007175</t>
+  </si>
+  <si>
+    <t>Rural Electrification Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE020B08ES7</t>
+  </si>
+  <si>
+    <t>INE01XX07042</t>
+  </si>
+  <si>
+    <t>INE020B08DT7</t>
+  </si>
+  <si>
+    <t>DME Development Ltd. **</t>
+  </si>
+  <si>
+    <t>INE0J7Q07108</t>
+  </si>
+  <si>
+    <t>INE909H08386</t>
+  </si>
+  <si>
+    <t>INE0J7Q07074</t>
+  </si>
+  <si>
+    <t>INE0J7Q07082</t>
+  </si>
+  <si>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
+  </si>
+  <si>
+    <t>INE0J7Q07066</t>
+  </si>
+  <si>
+    <t>Sheela Foam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE916U08012</t>
+  </si>
+  <si>
+    <t>INE0J7Q07041</t>
+  </si>
+  <si>
+    <t>INE916U08038</t>
+  </si>
+  <si>
+    <t>INE916U08020</t>
+  </si>
+  <si>
+    <t>INE0J7Q07090</t>
+  </si>
+  <si>
+    <t>INE813H07374</t>
+  </si>
+  <si>
+    <t>INE0J7Q07017</t>
+  </si>
+  <si>
+    <t>INE115A07QV7</t>
+  </si>
+  <si>
+    <t>INE261F08EO7</t>
+  </si>
+  <si>
+    <t>INE020B08EA5</t>
+  </si>
+  <si>
+    <t>INE020B08EM0</t>
+  </si>
+  <si>
+    <t>INE261F08EB4</t>
+  </si>
+  <si>
+    <t>INE233A08071</t>
+  </si>
+  <si>
+    <t>INE667F07JA5</t>
   </si>
   <si>
     <t>360 One Prime Ltd. **</t>
   </si>
   <si>
-    <t>INE248U07EQ0</t>
-  </si>
-  <si>
-    <t>Tata Capital Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE033L07HZ9</t>
-  </si>
-  <si>
-    <t>INE729N08089</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A07QY1</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd. **</t>
-  </si>
-  <si>
-    <t>INE775A08089</t>
-  </si>
-  <si>
-    <t>FITCH AAA</t>
-  </si>
-  <si>
-    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE128M08078</t>
-  </si>
-  <si>
-    <t>CRISIL AAA(CE)</t>
-  </si>
-  <si>
-    <t>INE115A07RB7</t>
-  </si>
-  <si>
-    <t>INE261F08EI9</t>
-  </si>
-  <si>
-    <t>Narayana Hrudayalaya Ltd. **</t>
-  </si>
-  <si>
-    <t>INE410P08016</t>
-  </si>
-  <si>
-    <t>ICRA AA</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE233A08121</t>
-  </si>
-  <si>
-    <t>Tata Motors Finance Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE477S08100</t>
-  </si>
-  <si>
-    <t>ICICI Home Finance Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE071G07777</t>
-  </si>
-  <si>
-    <t>INE115A07PW7</t>
-  </si>
-  <si>
-    <t>TMF Holdings Ltd. **</t>
-  </si>
-  <si>
-    <t>INE909H08311</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Financial Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE774D07UI4</t>
-  </si>
-  <si>
-    <t>SMFG India Credit Company Ltd **</t>
-  </si>
-  <si>
-    <t>INE535H07CK4</t>
-  </si>
-  <si>
-    <t>Altius Telecom Infrastructure Trust. **</t>
-  </si>
-  <si>
-    <t>INE0BWS08019</t>
-  </si>
-  <si>
-    <t>INE556F08KK5</t>
-  </si>
-  <si>
-    <t>INE915D08CX8</t>
-  </si>
-  <si>
-    <t>INE507T07096</t>
-  </si>
-  <si>
-    <t>INE115A07JW0</t>
-  </si>
-  <si>
-    <t>Titan Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE280A08023</t>
-  </si>
-  <si>
-    <t>INE280A08015</t>
-  </si>
-  <si>
-    <t>SMFG India Home Finance Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE213W07293</t>
-  </si>
-  <si>
-    <t>CARE AAA</t>
-  </si>
-  <si>
-    <t>Summit Digitel Infrastructure Ltd **</t>
-  </si>
-  <si>
-    <t>INE507T07062</t>
-  </si>
-  <si>
-    <t>INE115A07PV9</t>
-  </si>
-  <si>
-    <t>INE115A07NU6</t>
-  </si>
-  <si>
-    <t>Eris Lifesciences Ltd. **</t>
-  </si>
-  <si>
-    <t>INE406M08029</t>
-  </si>
-  <si>
-    <t>FITCH AA-</t>
-  </si>
-  <si>
-    <t>Rural Electrification Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE020B08ES7</t>
-  </si>
-  <si>
-    <t>INE233A08071</t>
-  </si>
-  <si>
-    <t>INE01XX07042</t>
-  </si>
-  <si>
-    <t>INE020B08DF6</t>
-  </si>
-  <si>
-    <t>DME Development Ltd. **</t>
-  </si>
-  <si>
-    <t>INE0J7Q07108</t>
-  </si>
-  <si>
-    <t>INE909H08386</t>
-  </si>
-  <si>
-    <t>INE0J7Q07074</t>
-  </si>
-  <si>
-    <t>INE0J7Q07082</t>
-  </si>
-  <si>
-    <t>INE0J7Q07066</t>
-  </si>
-  <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
-    <t>Sheela Foam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE916U08012</t>
-  </si>
-  <si>
-    <t>FITCH AA</t>
-  </si>
-  <si>
-    <t>INE0J7Q07041</t>
-  </si>
-  <si>
-    <t>INE916U08038</t>
-  </si>
-  <si>
-    <t>INE115A07MQ6</t>
-  </si>
-  <si>
-    <t>INE916U08046</t>
-  </si>
-  <si>
-    <t>INE916U08020</t>
-  </si>
-  <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
-    <t>INE0J7Q07090</t>
-  </si>
-  <si>
-    <t>INE0J7Q07017</t>
-  </si>
-  <si>
-    <t>INE813H07374</t>
-  </si>
-  <si>
-    <t>INE115A07QV7</t>
-  </si>
-  <si>
-    <t>INE020B08EA5</t>
-  </si>
-  <si>
     <t>INE248U07FA1</t>
   </si>
   <si>
-    <t>INE020B08EM0</t>
-  </si>
-  <si>
-    <t>INE261F08EB4</t>
-  </si>
-  <si>
     <t>INE033L07HF1</t>
   </si>
   <si>
@@ -565,75 +625,63 @@
     <t>CRISIL AA+(CE)</t>
   </si>
   <si>
-    <t>INE406M08011</t>
+    <t>INE020B08FA2</t>
+  </si>
+  <si>
+    <t>INE020B08FF1</t>
   </si>
   <si>
     <t>INE01XX07059</t>
   </si>
   <si>
-    <t>INE233A08063</t>
-  </si>
-  <si>
-    <t>INE020B08FF1</t>
+    <t>INE556F08KN9</t>
   </si>
   <si>
     <t>INE041007142</t>
   </si>
   <si>
+    <t>Cube Highways Trust **</t>
+  </si>
+  <si>
+    <t>INE0NR607058</t>
+  </si>
+  <si>
     <t>INE813H07192</t>
   </si>
   <si>
+    <t>INE115A07QZ8</t>
+  </si>
+  <si>
+    <t>INE020B08EW9</t>
+  </si>
+  <si>
     <t>INE115A07LO3</t>
   </si>
   <si>
-    <t>INE261F08DV4</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
     <t>INE134E08MC7</t>
   </si>
   <si>
-    <t>INE556F08KU4</t>
-  </si>
-  <si>
-    <t>Nexus Select Trust **</t>
+    <t>INE020B08FC8</t>
+  </si>
+  <si>
+    <t>INE115A07KM9</t>
+  </si>
+  <si>
+    <t>INE115A07RA9</t>
+  </si>
+  <si>
+    <t>INE134E08ML8</t>
+  </si>
+  <si>
+    <t>INE020B08ED9</t>
   </si>
   <si>
     <t>INE0NDH07019</t>
   </si>
   <si>
-    <t>INE115A07KM9</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd. ( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE090A08UD0</t>
-  </si>
-  <si>
-    <t>INE134E08ML8</t>
-  </si>
-  <si>
-    <t>INE115A07RA9</t>
-  </si>
-  <si>
-    <t>INE020B08ED9</t>
-  </si>
-  <si>
-    <t>INE134E08LO4</t>
-  </si>
-  <si>
     <t>INE909H08345</t>
   </si>
   <si>
-    <t>Chennai Petroleum Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE178A08029</t>
-  </si>
-  <si>
     <t>INE729N08030</t>
   </si>
   <si>
@@ -643,16 +691,28 @@
     <t>INE909H08394</t>
   </si>
   <si>
+    <t>INE556F08KP4</t>
+  </si>
+  <si>
     <t>INE403D08181</t>
   </si>
   <si>
+    <t>INE020B08AH8</t>
+  </si>
+  <si>
+    <t>INE020B08BG8</t>
+  </si>
+  <si>
     <t>INE134E08IE1</t>
   </si>
   <si>
-    <t>Rural Electrification Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE020B08BG8</t>
+    <t>INE556F08KQ2</t>
+  </si>
+  <si>
+    <t>INE261F08EK5</t>
+  </si>
+  <si>
+    <t>INE414G07JH5</t>
   </si>
   <si>
     <t>INE261F08BC8</t>
@@ -700,21 +760,21 @@
     <t>FITCH AAA(SO)</t>
   </si>
   <si>
+    <t>India Universal Trust AL2 **</t>
+  </si>
+  <si>
+    <t>INE1CBK15037</t>
+  </si>
+  <si>
+    <t>INE1CBK15029</t>
+  </si>
+  <si>
     <t>INE16J715019</t>
   </si>
   <si>
-    <t>India Universal Trust AL2 **</t>
-  </si>
-  <si>
     <t>INE1CBK15011</t>
   </si>
   <si>
-    <t>INE1CBK15037</t>
-  </si>
-  <si>
-    <t>INE1CBK15029</t>
-  </si>
-  <si>
     <t>INE16J715027</t>
   </si>
   <si>
@@ -733,21 +793,15 @@
     <t>Certificate of Deposits</t>
   </si>
   <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A16PE2</t>
+    <t>Export-Import Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE514E16CL5</t>
   </si>
   <si>
     <t>CRISIL A1+</t>
   </si>
   <si>
-    <t>HDFC Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE040A16FU3</t>
-  </si>
-  <si>
     <t>Commercial Papers</t>
   </si>
   <si>
@@ -778,6 +832,42 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -25-Apr-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -25-Apr-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -06-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -796,7 +886,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -809,10 +899,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - NIFTY Short Duration
-Debt Index  A-II</t>
   </si>
 </sst>
 </file>
@@ -901,7 +987,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -987,6 +1073,14 @@
         <color auto="1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1013,7 +1107,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1095,6 +1189,9 @@
       <protection/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1195,13 +1292,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>199</xdr:row>
+      <xdr:row>233</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>209</xdr:row>
+      <xdr:row>243</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1219,8 +1316,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="38947725"/>
-          <a:ext cx="3657600" cy="1905000"/>
+          <a:off x="666750" y="45253275"/>
+          <a:ext cx="6419850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1234,13 +1331,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>214</xdr:row>
+      <xdr:row>248</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>224</xdr:row>
+      <xdr:row>258</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1258,8 +1355,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="41805225"/>
-          <a:ext cx="3657600" cy="1905000"/>
+          <a:off x="666750" y="48110775"/>
+          <a:ext cx="6419850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1592,19 +1689,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J213"/>
+  <dimension ref="B1:J246"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="23" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="23" width="54.857142857142854" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="17.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="23" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="23" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="23" width="13.714285714285714" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="23" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="23" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="23" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="23" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="24" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="24" width="96.28571428571429" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="24" width="17.142857142857142" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="24" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="24" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="24" width="13.714285714285714" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="24" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="24" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="24" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="24" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1692,10 +1789,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>1907345.2299999988</v>
+        <v>2023376.7199999993</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9609890258541003</v>
+        <v>0.9506785310015002</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1729,10 +1826,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>1793114.4099999992</v>
+        <v>1923060.4999999995</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9034354363372004</v>
+        <v>0.9035452039633003</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1766,10 +1863,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>581107.8300000002</v>
+        <v>482850.52</v>
       </c>
       <c r="H9" s="10">
-        <v>0.29278299423039994</v>
+        <v>0.22686611865790002</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1792,16 +1889,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>245555180</v>
+        <v>130385280</v>
       </c>
       <c r="G10" s="16">
-        <v>251464.22</v>
+        <v>137449.55</v>
       </c>
       <c r="H10" s="17">
-        <v>0.1266967049361</v>
+        <v>0.064580329995</v>
       </c>
       <c r="I10" s="16">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1815,22 +1912,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="14">
-        <v>7.930000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="15">
-        <v>134986450</v>
+        <v>120951240</v>
       </c>
       <c r="G11" s="16">
-        <v>138444.26</v>
+        <v>125600.85</v>
       </c>
       <c r="H11" s="17">
-        <v>0.0697531901728</v>
+        <v>0.0590132477018</v>
       </c>
       <c r="I11" s="16">
-        <v>7.66</v>
+        <v>7.31</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1844,22 +1941,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="14">
-        <v>7.53</v>
+        <v>6.99</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="15">
-        <v>86074740</v>
+        <v>69574740</v>
       </c>
       <c r="G12" s="16">
-        <v>86701.97</v>
+        <v>71019.39</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0436835662364</v>
+        <v>0.0333682841613</v>
       </c>
       <c r="I12" s="16">
-        <v>7.47</v>
+        <v>6.80</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1873,22 +1970,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>7.06</v>
+        <v>6.79</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="15">
-        <v>53854250</v>
+        <v>41814710</v>
       </c>
       <c r="G13" s="16">
-        <v>54523.07</v>
+        <v>43317.07</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0274706807672</v>
+        <v>0.0203524178509</v>
       </c>
       <c r="I13" s="16">
-        <v>6.73</v>
+        <v>6.37</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1902,22 +1999,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="14">
-        <v>7.17</v>
+        <v>6.640000000000001</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="15">
-        <v>21500000</v>
+        <v>20000000</v>
       </c>
       <c r="G14" s="16">
-        <v>21964.79</v>
+        <v>20520.1</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0110666500292</v>
+        <v>0.0096413180656</v>
       </c>
       <c r="I14" s="16">
-        <v>6.78</v>
+        <v>6.39</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1931,22 +2028,22 @@
         <v>22</v>
       </c>
       <c r="D15" s="14">
-        <v>7.02</v>
+        <v>7.34</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="15">
-        <v>10000000</v>
+        <v>16507500</v>
       </c>
       <c r="G15" s="16">
-        <v>10161.14</v>
+        <v>17571.14</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0051195472516</v>
+        <v>0.0082557565273</v>
       </c>
       <c r="I15" s="16">
-        <v>6.82</v>
+        <v>6.98</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1954,28 +2051,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="14">
-        <v>6.79</v>
+        <v>7.12</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="15">
-        <v>9650850</v>
+        <v>13228600</v>
       </c>
       <c r="G16" s="16">
-        <v>9714.51</v>
+        <v>13673.60</v>
       </c>
       <c r="H16" s="17">
-        <v>0.0048945190177</v>
+        <v>0.0064245070298</v>
       </c>
       <c r="I16" s="16">
-        <v>6.81</v>
+        <v>6.83</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1983,28 +2080,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" s="14">
-        <v>7.18</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="15">
-        <v>3739410</v>
+        <v>12000000</v>
       </c>
       <c r="G17" s="16">
-        <v>3841.66</v>
+        <v>12453.06</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0019355662745</v>
+        <v>0.0058510393395</v>
       </c>
       <c r="I17" s="16">
-        <v>6.87</v>
+        <v>6.82</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -2012,28 +2109,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18" s="14">
-        <v>7.26</v>
+        <v>7.32</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="15">
-        <v>2434500</v>
+        <v>11051200</v>
       </c>
       <c r="G18" s="16">
-        <v>2510.49</v>
+        <v>11599.64</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0012648750218</v>
+        <v>0.0054500620702</v>
       </c>
       <c r="I18" s="16">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -2041,28 +2138,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14">
-        <v>7.86</v>
+        <v>7.17</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="15">
-        <v>500000</v>
+        <v>10000000</v>
       </c>
       <c r="G19" s="16">
-        <v>512.43</v>
+        <v>10538.96</v>
       </c>
       <c r="H19" s="17">
-        <v>0.000258180637</v>
+        <v>0.0049517042042</v>
       </c>
       <c r="I19" s="16">
-        <v>7.02</v>
+        <v>5.97</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -2070,28 +2167,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="14">
-        <v>7.59</v>
+        <v>7.02</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="15">
-        <v>500000</v>
+        <v>10000000</v>
       </c>
       <c r="G20" s="16">
-        <v>508.29</v>
+        <v>10512.05</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0002560947563</v>
+        <v>0.0049390606075</v>
       </c>
       <c r="I20" s="16">
-        <v>7.03</v>
+        <v>6.09</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -2099,28 +2196,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="14">
-        <v>7.33</v>
+        <v>7.13</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F21" s="15">
-        <v>337800</v>
+        <v>4659200</v>
       </c>
       <c r="G21" s="16">
-        <v>341.63</v>
+        <v>4812.72</v>
       </c>
       <c r="H21" s="17">
-        <v>0.000172125463</v>
+        <v>0.0022612445495</v>
       </c>
       <c r="I21" s="16">
-        <v>6.73</v>
+        <v>6.75</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -2128,28 +2225,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D22" s="14">
-        <v>7.06</v>
+        <v>7.29</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="15">
-        <v>300800</v>
+        <v>1733000</v>
       </c>
       <c r="G22" s="16">
-        <v>301.67</v>
+        <v>1809.01</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0001519921799</v>
+        <v>0.0008499588595</v>
       </c>
       <c r="I22" s="16">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -2157,28 +2254,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D23" s="14">
-        <v>7.08</v>
+        <v>7.86</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="15">
-        <v>61700</v>
+        <v>500000</v>
       </c>
       <c r="G23" s="16">
-        <v>61.93</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>34</v>
+        <v>522.14</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0.0002453261833</v>
       </c>
       <c r="I23" s="16">
-        <v>6.98</v>
+        <v>6.06</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -2186,28 +2283,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>7.38</v>
+        <v>7.59</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="15">
-        <v>42900</v>
+        <v>500000</v>
       </c>
       <c r="G24" s="16">
-        <v>43.21</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>34</v>
+        <v>517.75</v>
+      </c>
+      <c r="H24" s="17">
+        <v>0.0002432635527</v>
       </c>
       <c r="I24" s="16">
-        <v>7</v>
+        <v>6.07</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -2218,25 +2315,25 @@
         <v>15</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D25" s="14">
-        <v>6.92</v>
+        <v>7.33</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F25" s="15">
-        <v>12450</v>
+        <v>337800</v>
       </c>
       <c r="G25" s="16">
-        <v>12.56</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>34</v>
+        <v>345.29</v>
+      </c>
+      <c r="H25" s="17">
+        <v>0.0001622336496</v>
       </c>
       <c r="I25" s="16">
-        <v>6.94</v>
+        <v>5.75</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -2244,36 +2341,57 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>13</v>
+        <v>34</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="14">
+        <v>7.06</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="15">
+        <v>300800</v>
+      </c>
+      <c r="G26" s="16">
+        <v>306</v>
+      </c>
+      <c r="H26" s="17">
+        <v>0.0001437733406</v>
+      </c>
+      <c r="I26" s="16">
+        <v>5.95</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
-      <c r="B27" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="9">
-        <v>1199791.7300000004</v>
-      </c>
-      <c r="H27" s="10">
-        <v>0.6044981620018001</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>13</v>
+      <c r="B27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14">
+        <v>7.26</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="15">
+        <v>96000</v>
+      </c>
+      <c r="G27" s="16">
+        <v>102.07</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="16">
+        <v>6.31</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -2281,28 +2399,28 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D28" s="14">
-        <v>7.58</v>
+        <v>6.92</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F28" s="15">
-        <v>55000</v>
+        <v>70350</v>
       </c>
       <c r="G28" s="16">
-        <v>54924.21</v>
-      </c>
-      <c r="H28" s="17">
-        <v>0.0276727895054</v>
+        <v>73.66</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>41</v>
       </c>
       <c r="I28" s="16">
-        <v>7.63</v>
+        <v>6.52</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -2310,28 +2428,28 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="14">
+        <v>7.08</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="15">
+        <v>61700</v>
+      </c>
+      <c r="G29" s="16">
+        <v>62.77</v>
+      </c>
+      <c r="H29" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="14">
-        <v>7.55</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="15">
-        <v>37000</v>
-      </c>
-      <c r="G29" s="16">
-        <v>36943.39</v>
-      </c>
-      <c r="H29" s="17">
-        <v>0.0186134066396</v>
-      </c>
       <c r="I29" s="16">
-        <v>7.61</v>
+        <v>5.97</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
@@ -2339,28 +2457,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="14">
+        <v>7.38</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="15">
+        <v>42900</v>
+      </c>
+      <c r="G30" s="16">
+        <v>43.70</v>
+      </c>
+      <c r="H30" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="14">
-        <v>7.43</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="15">
-        <v>36500</v>
-      </c>
-      <c r="G30" s="16">
-        <v>36365.64</v>
-      </c>
-      <c r="H30" s="17">
-        <v>0.0183223154407</v>
-      </c>
       <c r="I30" s="16">
-        <v>7.64</v>
+        <v>5.94</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -2368,57 +2486,36 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="14">
-        <v>7.50</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="15">
-        <v>35000</v>
-      </c>
-      <c r="G31" s="16">
-        <v>34916.21</v>
-      </c>
-      <c r="H31" s="17">
-        <v>0.0175920405529</v>
-      </c>
-      <c r="I31" s="16">
-        <v>7.62</v>
+        <v>13</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
-      <c r="B32" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="14">
-        <v>7.53</v>
-      </c>
-      <c r="E32" s="13" t="s">
+      <c r="B32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="15">
-        <v>33000</v>
-      </c>
-      <c r="G32" s="16">
-        <v>33039.24</v>
-      </c>
-      <c r="H32" s="17">
-        <v>0.0166463556588</v>
-      </c>
-      <c r="I32" s="16">
-        <v>7.50</v>
+      <c r="C32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="9">
+        <v>1427551.81</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0.6707316755414001</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
@@ -2432,22 +2529,22 @@
         <v>48</v>
       </c>
       <c r="D33" s="14">
-        <v>8.85</v>
+        <v>7.58</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F33" s="15">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="G33" s="16">
-        <v>30094.26</v>
+        <v>61500.06</v>
       </c>
       <c r="H33" s="17">
-        <v>0.015162568971</v>
+        <v>0.0288956505824</v>
       </c>
       <c r="I33" s="16">
-        <v>8.63</v>
+        <v>7.21</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2461,22 +2558,22 @@
         <v>51</v>
       </c>
       <c r="D34" s="14">
-        <v>7.82</v>
+        <v>7.58</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F34" s="15">
-        <v>3000</v>
+        <v>55000</v>
       </c>
       <c r="G34" s="16">
-        <v>29988</v>
+        <v>55555.12</v>
       </c>
       <c r="H34" s="17">
-        <v>0.0151090313668</v>
+        <v>0.0261024352754</v>
       </c>
       <c r="I34" s="16">
-        <v>7.84</v>
+        <v>6.62</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
@@ -2490,22 +2587,22 @@
         <v>53</v>
       </c>
       <c r="D35" s="14">
-        <v>7.75</v>
+        <v>7.53</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F35" s="15">
-        <v>3000</v>
+        <v>50500</v>
       </c>
       <c r="G35" s="16">
-        <v>29965.89</v>
+        <v>51638.88</v>
       </c>
       <c r="H35" s="17">
-        <v>0.0150978915548</v>
+        <v>0.0242623996293</v>
       </c>
       <c r="I35" s="16">
-        <v>7.84</v>
+        <v>6.61</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2513,28 +2610,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D36" s="14">
-        <v>7.87</v>
+        <v>7.55</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F36" s="15">
-        <v>28300</v>
+        <v>37000</v>
       </c>
       <c r="G36" s="16">
-        <v>28502.63</v>
+        <v>37404.3</v>
       </c>
       <c r="H36" s="17">
-        <v>0.0143606486163</v>
+        <v>0.0175743175385</v>
       </c>
       <c r="I36" s="16">
-        <v>7.92</v>
+        <v>6.61</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -2542,28 +2639,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D37" s="14">
-        <v>7.96</v>
+        <v>7.43</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F37" s="15">
-        <v>25300</v>
+        <v>36500</v>
       </c>
       <c r="G37" s="16">
-        <v>25585</v>
+        <v>36832</v>
       </c>
       <c r="H37" s="17">
-        <v>0.0128906418407</v>
+        <v>0.0173054238037</v>
       </c>
       <c r="I37" s="16">
-        <v>7.84</v>
+        <v>6.61</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2571,28 +2668,28 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>59</v>
-      </c>
       <c r="D38" s="14">
-        <v>8.75</v>
+        <v>7.50</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F38" s="15">
-        <v>25000</v>
+        <v>35000</v>
       </c>
       <c r="G38" s="16">
-        <v>24988.13</v>
+        <v>35342.93</v>
       </c>
       <c r="H38" s="17">
-        <v>0.0125899172992</v>
+        <v>0.0166057879592</v>
       </c>
       <c r="I38" s="16">
-        <v>8.77</v>
+        <v>6.62</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
@@ -2600,28 +2697,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D39" s="14">
-        <v>8.65</v>
+        <v>7.42</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F39" s="15">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="G39" s="16">
-        <v>24983.88</v>
+        <v>30649.71</v>
       </c>
       <c r="H39" s="17">
-        <v>0.0125877759966</v>
+        <v>0.0144006901881</v>
       </c>
       <c r="I39" s="16">
-        <v>8.68</v>
+        <v>6.56</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2629,28 +2726,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" s="14">
+        <v>8.85</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" s="14">
-        <v>8.950000000000001</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="F40" s="15">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G40" s="16">
-        <v>20189.02</v>
+        <v>30313.32</v>
       </c>
       <c r="H40" s="17">
-        <v>0.0101719533295</v>
+        <v>0.0142426381814</v>
       </c>
       <c r="I40" s="16">
-        <v>8.35</v>
+        <v>8.03</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2658,28 +2755,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="D41" s="14">
-        <v>8.40</v>
+        <v>7.87</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F41" s="15">
-        <v>20000</v>
+        <v>28300</v>
       </c>
       <c r="G41" s="16">
-        <v>20046.14</v>
+        <v>29308.19</v>
       </c>
       <c r="H41" s="17">
-        <v>0.0100999652542</v>
+        <v>0.013770380345</v>
       </c>
       <c r="I41" s="16">
-        <v>8.3</v>
+        <v>7.15</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2687,28 +2784,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D42" s="14">
-        <v>8.17</v>
+        <v>7.44</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F42" s="15">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="G42" s="16">
-        <v>20027.82</v>
+        <v>26554.50</v>
       </c>
       <c r="H42" s="17">
-        <v>0.0100907349803</v>
+        <v>0.0124765659316</v>
       </c>
       <c r="I42" s="16">
-        <v>8.17</v>
+        <v>6.59</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2716,28 +2813,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="D43" s="14">
-        <v>8.03</v>
+        <v>7.96</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F43" s="15">
-        <v>20000</v>
+        <v>25300</v>
       </c>
       <c r="G43" s="16">
-        <v>20008.02</v>
+        <v>26219.91</v>
       </c>
       <c r="H43" s="17">
-        <v>0.0100807590292</v>
+        <v>0.0123193596504</v>
       </c>
       <c r="I43" s="16">
-        <v>8.15</v>
+        <v>6.98</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2745,28 +2842,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="14">
+        <v>8.75</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" s="14">
-        <v>7.640000000000001</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F44" s="15">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="G44" s="16">
-        <v>19991.9</v>
+        <v>25421.05</v>
       </c>
       <c r="H44" s="17">
-        <v>0.0100726371943</v>
+        <v>0.0119440172617</v>
       </c>
       <c r="I44" s="16">
-        <v>7.62</v>
+        <v>7.99</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2774,28 +2871,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D45" s="14">
-        <v>9.40</v>
+        <v>8.65</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F45" s="15">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="G45" s="16">
-        <v>19977.26</v>
+        <v>25299.98</v>
       </c>
       <c r="H45" s="17">
-        <v>0.0100652610365</v>
+        <v>0.0118871328226</v>
       </c>
       <c r="I45" s="16">
-        <v>9.7</v>
+        <v>8.10</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2803,28 +2900,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D46" s="14">
-        <v>8</v>
+        <v>7.74</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F46" s="15">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="G46" s="16">
-        <v>19943.70</v>
+        <v>21402.26</v>
       </c>
       <c r="H46" s="17">
-        <v>0.0100483523033</v>
+        <v>0.0100557987526</v>
       </c>
       <c r="I46" s="16">
-        <v>8.38</v>
+        <v>6.92</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2832,28 +2929,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D47" s="14">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F47" s="15">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="G47" s="16">
-        <v>19855.08</v>
+        <v>20494.38</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0100037023646</v>
+        <v>0.0096292335874</v>
       </c>
       <c r="I47" s="16">
-        <v>7.94</v>
+        <v>6.55</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2861,28 +2958,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D48" s="14">
-        <v>7.58</v>
+        <v>8.950000000000001</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F48" s="15">
-        <v>1900</v>
+        <v>20000</v>
       </c>
       <c r="G48" s="16">
-        <v>18975</v>
+        <v>20359.78</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0095602864541</v>
+        <v>0.0095659921114</v>
       </c>
       <c r="I48" s="16">
-        <v>7.72</v>
+        <v>7.59</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2890,28 +2987,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D49" s="14">
-        <v>7.57</v>
+        <v>8.40</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F49" s="15">
-        <v>18500</v>
+        <v>20000</v>
       </c>
       <c r="G49" s="16">
-        <v>18472.1</v>
+        <v>20325.06</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0093069073733</v>
+        <v>0.0095496790056</v>
       </c>
       <c r="I49" s="16">
-        <v>7.69</v>
+        <v>7.38</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2919,28 +3016,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D50" s="14">
-        <v>8.700000000000001</v>
+        <v>8</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="F50" s="15">
-        <v>1550</v>
+        <v>20000</v>
       </c>
       <c r="G50" s="16">
-        <v>15523.64</v>
+        <v>20264.36</v>
       </c>
       <c r="H50" s="17">
-        <v>0.0078213673365</v>
+        <v>0.0095211592612</v>
       </c>
       <c r="I50" s="16">
-        <v>8.39</v>
+        <v>7.56</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2948,28 +3045,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>83</v>
       </c>
       <c r="D51" s="14">
-        <v>7.50</v>
+        <v>7.640000000000001</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F51" s="15">
-        <v>1500</v>
+        <v>20000</v>
       </c>
       <c r="G51" s="16">
-        <v>14959.37</v>
+        <v>20241.70</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0075370678457</v>
+        <v>0.0095105125164</v>
       </c>
       <c r="I51" s="16">
-        <v>7.75</v>
+        <v>6.55</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2977,28 +3074,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D52" s="14">
-        <v>7.40</v>
+        <v>7.19</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F52" s="15">
-        <v>1500</v>
+        <v>20000</v>
       </c>
       <c r="G52" s="16">
-        <v>14954.60</v>
+        <v>20121.82</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0075346645484</v>
+        <v>0.0094541871959</v>
       </c>
       <c r="I52" s="16">
-        <v>7.72</v>
+        <v>7.08</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -3006,28 +3103,28 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D53" s="14">
-        <v>8.40</v>
+        <v>7.27</v>
       </c>
       <c r="E53" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F53" s="15">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="G53" s="16">
-        <v>14135.65</v>
+        <v>20089.50</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0071220481272</v>
+        <v>0.0094390017241</v>
       </c>
       <c r="I53" s="16">
-        <v>8.02</v>
+        <v>7.09</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -3035,28 +3132,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D54" s="14">
-        <v>7.9123</v>
+        <v>7.35</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F54" s="15">
-        <v>13500</v>
+        <v>2000</v>
       </c>
       <c r="G54" s="16">
-        <v>13512.27</v>
+        <v>20081.54</v>
       </c>
       <c r="H54" s="17">
-        <v>0.0068079668956</v>
+        <v>0.0094352617379</v>
       </c>
       <c r="I54" s="16">
-        <v>7.83</v>
+        <v>7.22</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -3064,28 +3161,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D55" s="14">
-        <v>7.44</v>
+        <v>9.40</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="F55" s="15">
-        <v>13500</v>
+        <v>20000</v>
       </c>
       <c r="G55" s="16">
-        <v>13488</v>
+        <v>20076.48</v>
       </c>
       <c r="H55" s="17">
-        <v>0.006795738798</v>
+        <v>0.0094328843094</v>
       </c>
       <c r="I55" s="16">
-        <v>7.47</v>
+        <v>9.21</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -3093,28 +3190,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D56" s="14">
-        <v>8.3</v>
+        <v>8.17</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F56" s="15">
-        <v>13500</v>
+        <v>20000</v>
       </c>
       <c r="G56" s="16">
-        <v>13465.41</v>
+        <v>20072</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0067843571447</v>
+        <v>0.0094307793925</v>
       </c>
       <c r="I56" s="16">
-        <v>9.09</v>
+        <v>6.95</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -3122,28 +3219,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D57" s="14">
-        <v>9.40</v>
+        <v>8.03</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="F57" s="15">
-        <v>1300</v>
+        <v>20000</v>
       </c>
       <c r="G57" s="16">
-        <v>13171.86</v>
+        <v>20001.70</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0066364561124</v>
+        <v>0.009397749112</v>
       </c>
       <c r="I57" s="16">
-        <v>8.51</v>
+        <v>6.90</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -3151,28 +3248,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="D58" s="14">
-        <v>8.50</v>
+        <v>7.51</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="F58" s="15">
-        <v>12500</v>
+        <v>19500</v>
       </c>
       <c r="G58" s="16">
-        <v>12602.98</v>
+        <v>19974.53</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0063498339381</v>
+        <v>0.0093849833549</v>
       </c>
       <c r="I58" s="16">
-        <v>8.04</v>
+        <v>6.59</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -3180,28 +3277,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D59" s="14">
-        <v>7.44</v>
+        <v>7.58</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F59" s="15">
-        <v>12500</v>
+        <v>1900</v>
       </c>
       <c r="G59" s="16">
-        <v>12461.05</v>
+        <v>19109.17</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0062783245069</v>
+        <v>0.0089783961062</v>
       </c>
       <c r="I59" s="16">
-        <v>7.61</v>
+        <v>6.53</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -3209,28 +3306,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D60" s="14">
-        <v>9.41</v>
+        <v>7.70</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="F60" s="15">
-        <v>1230000</v>
+        <v>15000</v>
       </c>
       <c r="G60" s="16">
-        <v>12307.32</v>
+        <v>15341.52</v>
       </c>
       <c r="H60" s="17">
-        <v>0.0062008698119</v>
+        <v>0.0072081751029</v>
       </c>
       <c r="I60" s="16">
-        <v>9.34</v>
+        <v>6.59</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -3238,28 +3335,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D61" s="14">
-        <v>7.9613000000000005</v>
+        <v>7.34</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F61" s="15">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="G61" s="16">
-        <v>12027.76</v>
+        <v>15332.06</v>
       </c>
       <c r="H61" s="17">
-        <v>0.006060017444</v>
+        <v>0.0072037303454</v>
       </c>
       <c r="I61" s="16">
-        <v>7.80</v>
+        <v>6.65</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -3267,28 +3364,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D62" s="14">
-        <v>9.50</v>
+        <v>8.40</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="F62" s="15">
-        <v>115</v>
+        <v>14000</v>
       </c>
       <c r="G62" s="16">
-        <v>11747.33</v>
+        <v>14384.59</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0059187267389</v>
+        <v>0.006758563917</v>
       </c>
       <c r="I62" s="16">
-        <v>8.64</v>
+        <v>7.19</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -3296,28 +3393,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>104</v>
-      </c>
       <c r="D63" s="14">
-        <v>7.57</v>
+        <v>7.9123</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F63" s="15">
-        <v>11000</v>
+        <v>13500</v>
       </c>
       <c r="G63" s="16">
-        <v>10972.63</v>
+        <v>13660.68</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0055284050569</v>
+        <v>0.0064184365998</v>
       </c>
       <c r="I63" s="16">
-        <v>7.62</v>
+        <v>7</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3325,28 +3422,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>106</v>
-      </c>
       <c r="D64" s="14">
-        <v>8.15</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="F64" s="15">
-        <v>10500</v>
+        <v>13500</v>
       </c>
       <c r="G64" s="16">
-        <v>10523.10</v>
+        <v>13494.52</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0053019156988</v>
+        <v>0.0063403667361</v>
       </c>
       <c r="I64" s="16">
-        <v>7.89</v>
+        <v>7.90</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3354,28 +3451,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D65" s="14">
-        <v>6.58</v>
+        <v>9.40</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="F65" s="15">
-        <v>1050</v>
+        <v>1300</v>
       </c>
       <c r="G65" s="16">
-        <v>10338.96</v>
+        <v>13207.26</v>
       </c>
       <c r="H65" s="17">
-        <v>0.0052091393537</v>
+        <v>0.006205398338</v>
       </c>
       <c r="I65" s="16">
-        <v>7.89</v>
+        <v>8.01</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3383,28 +3480,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D66" s="14">
-        <v>7.58</v>
+        <v>9.05</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F66" s="15">
-        <v>10000</v>
+        <v>12900</v>
       </c>
       <c r="G66" s="16">
-        <v>10040.33</v>
+        <v>13204.40</v>
       </c>
       <c r="H66" s="17">
-        <v>0.0050586788349</v>
+        <v>0.0062040545741</v>
       </c>
       <c r="I66" s="16">
-        <v>7.52</v>
+        <v>8.56</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3412,28 +3509,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D67" s="14">
-        <v>7.70</v>
+        <v>7.80</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F67" s="15">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="G67" s="16">
-        <v>10035.75</v>
+        <v>12745.64</v>
       </c>
       <c r="H67" s="17">
-        <v>0.0050563712665</v>
+        <v>0.0059885073264</v>
       </c>
       <c r="I67" s="16">
-        <v>7.52</v>
+        <v>6.57</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3441,28 +3538,28 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" s="14">
+        <v>8.50</v>
+      </c>
+      <c r="E68" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" s="14">
-        <v>8.25</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>115</v>
-      </c>
       <c r="F68" s="15">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="G68" s="16">
-        <v>10027.53</v>
+        <v>12708.29</v>
       </c>
       <c r="H68" s="17">
-        <v>0.0050522297353</v>
+        <v>0.0059709585216</v>
       </c>
       <c r="I68" s="16">
-        <v>8.09</v>
+        <v>7.40</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -3470,28 +3567,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D69" s="14">
-        <v>8.36</v>
+        <v>7.44</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F69" s="15">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="G69" s="16">
-        <v>10019.04</v>
+        <v>12616.01</v>
       </c>
       <c r="H69" s="17">
-        <v>0.0050479521683</v>
+        <v>0.0059276009926</v>
       </c>
       <c r="I69" s="16">
-        <v>8.17</v>
+        <v>6.61</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3499,28 +3596,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D70" s="14">
-        <v>7.48</v>
+        <v>7.40</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="F70" s="15">
-        <v>1000</v>
+        <v>12500</v>
       </c>
       <c r="G70" s="16">
-        <v>9993.94</v>
+        <v>12481.18</v>
       </c>
       <c r="H70" s="17">
-        <v>0.0050353058869</v>
+        <v>0.0058642514517</v>
       </c>
       <c r="I70" s="16">
-        <v>7.86</v>
+        <v>7.46</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
@@ -3528,28 +3625,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D71" s="14">
-        <v>8.14</v>
+        <v>9.41</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="F71" s="15">
-        <v>10000</v>
+        <v>1230000</v>
       </c>
       <c r="G71" s="16">
-        <v>9988.24</v>
+        <v>12347.67</v>
       </c>
       <c r="H71" s="17">
-        <v>0.0050324340222</v>
+        <v>0.0058015221095</v>
       </c>
       <c r="I71" s="16">
-        <v>8.42</v>
+        <v>8.50</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3557,28 +3654,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D72" s="14">
-        <v>7.61</v>
+        <v>7.9613000000000005</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F72" s="15">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="G72" s="16">
-        <v>9976.62</v>
+        <v>12115.57</v>
       </c>
       <c r="H72" s="17">
-        <v>0.0050265794489</v>
+        <v>0.0056924705004</v>
       </c>
       <c r="I72" s="16">
-        <v>7.80</v>
+        <v>6.85</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3586,28 +3683,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D73" s="14">
-        <v>7.7541</v>
+        <v>9.50</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F73" s="15">
-        <v>1000</v>
+        <v>115</v>
       </c>
       <c r="G73" s="16">
-        <v>9935.90</v>
+        <v>11873.53</v>
       </c>
       <c r="H73" s="17">
-        <v>0.0050060632505</v>
+        <v>0.005578748607</v>
       </c>
       <c r="I73" s="16">
-        <v>8.45</v>
+        <v>8.11</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3615,28 +3712,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D74" s="14">
-        <v>8.11</v>
+        <v>7.79</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="F74" s="15">
-        <v>900</v>
+        <v>11500</v>
       </c>
       <c r="G74" s="16">
-        <v>9000.05</v>
+        <v>11740.78</v>
       </c>
       <c r="H74" s="17">
-        <v>0.0045345484111</v>
+        <v>0.0055163763489</v>
       </c>
       <c r="I74" s="16">
-        <v>7.78</v>
+        <v>6.57</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3644,28 +3741,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D75" s="14">
-        <v>8.28</v>
+        <v>7.57</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F75" s="15">
-        <v>8500</v>
+        <v>11000</v>
       </c>
       <c r="G75" s="16">
-        <v>8524.40</v>
+        <v>11255.94</v>
       </c>
       <c r="H75" s="17">
-        <v>0.004294898859</v>
+        <v>0.005288575478</v>
       </c>
       <c r="I75" s="16">
-        <v>8.01</v>
+        <v>6.92</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
@@ -3673,28 +3770,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D76" s="14">
-        <v>8.40</v>
+        <v>8.15</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F76" s="15">
-        <v>8500</v>
+        <v>10500</v>
       </c>
       <c r="G76" s="16">
-        <v>8517.68</v>
+        <v>10565.97</v>
       </c>
       <c r="H76" s="17">
-        <v>0.0042915130816</v>
+        <v>0.0049643947857</v>
       </c>
       <c r="I76" s="16">
-        <v>8.50</v>
+        <v>6.94</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3702,28 +3799,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D77" s="14">
-        <v>7.79</v>
+        <v>8.700000000000001</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F77" s="15">
-        <v>8000</v>
+        <v>1050</v>
       </c>
       <c r="G77" s="16">
-        <v>8042.75</v>
+        <v>10541.62</v>
       </c>
       <c r="H77" s="17">
-        <v>0.0040522262913</v>
+        <v>0.0049529539986</v>
       </c>
       <c r="I77" s="16">
-        <v>7.52</v>
+        <v>7.58</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3731,28 +3828,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D78" s="14">
-        <v>8.43</v>
+        <v>6.58</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="F78" s="15">
-        <v>8000</v>
+        <v>1050</v>
       </c>
       <c r="G78" s="16">
-        <v>7988.11</v>
+        <v>10476.17</v>
       </c>
       <c r="H78" s="17">
-        <v>0.004024696697</v>
+        <v>0.0049222024785</v>
       </c>
       <c r="I78" s="16">
-        <v>9.10</v>
+        <v>6.81</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3760,28 +3857,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D79" s="14">
-        <v>8.05</v>
+        <v>7.83</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F79" s="15">
-        <v>750</v>
+        <v>10000</v>
       </c>
       <c r="G79" s="16">
-        <v>7561.43</v>
+        <v>10367.42</v>
       </c>
       <c r="H79" s="17">
-        <v>0.0038097199896</v>
+        <v>0.0048711065608</v>
       </c>
       <c r="I79" s="16">
-        <v>7.89</v>
+        <v>6.59</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
@@ -3789,28 +3886,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D80" s="14">
-        <v>8.43</v>
+        <v>7.58</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F80" s="15">
-        <v>750</v>
+        <v>10000</v>
       </c>
       <c r="G80" s="16">
-        <v>7560.65</v>
+        <v>10293.26</v>
       </c>
       <c r="H80" s="17">
-        <v>0.0038093269975</v>
+        <v>0.0048362626689</v>
       </c>
       <c r="I80" s="16">
-        <v>7.76</v>
+        <v>7.14</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
@@ -3818,28 +3915,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D81" s="14">
-        <v>7.75</v>
+        <v>8.10</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F81" s="15">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="G81" s="16">
-        <v>7497.89</v>
+        <v>10280.82</v>
       </c>
       <c r="H81" s="17">
-        <v>0.0037777062556</v>
+        <v>0.0048304177657</v>
       </c>
       <c r="I81" s="16">
-        <v>7.72</v>
+        <v>7.11</v>
       </c>
       <c r="J81" s="11" t="s">
         <v>13</v>
@@ -3847,28 +3944,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="D82" s="14">
-        <v>7.75</v>
+        <v>8.36</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F82" s="15">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="G82" s="16">
-        <v>7493.18</v>
+        <v>10118.53</v>
       </c>
       <c r="H82" s="17">
-        <v>0.0037753331885</v>
+        <v>0.004754166212</v>
       </c>
       <c r="I82" s="16">
-        <v>7.73</v>
+        <v>7.28</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>13</v>
@@ -3876,28 +3973,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" s="14">
+        <v>8.25</v>
+      </c>
+      <c r="E83" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C83" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D83" s="14">
-        <v>8.07</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>140</v>
-      </c>
       <c r="F83" s="15">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="G83" s="16">
-        <v>7489.85</v>
+        <v>10108.26</v>
       </c>
       <c r="H83" s="17">
-        <v>0.0037736554149</v>
+        <v>0.0047493408779</v>
       </c>
       <c r="I83" s="16">
-        <v>8.10</v>
+        <v>7.55</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>13</v>
@@ -3905,28 +4002,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D84" s="14">
+        <v>8.60</v>
+      </c>
+      <c r="E84" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C84" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D84" s="14">
-        <v>6.59</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F84" s="15">
-        <v>750</v>
+        <v>10000</v>
       </c>
       <c r="G84" s="16">
-        <v>7396.28</v>
+        <v>10095.54</v>
       </c>
       <c r="H84" s="17">
-        <v>0.0037265114885</v>
+        <v>0.0047433644175</v>
       </c>
       <c r="I84" s="16">
-        <v>7.89</v>
+        <v>7.93</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>13</v>
@@ -3934,28 +4031,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>143</v>
       </c>
       <c r="D85" s="14">
-        <v>7.90</v>
+        <v>7.19</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F85" s="15">
-        <v>700</v>
+        <v>10000</v>
       </c>
       <c r="G85" s="16">
-        <v>7022.41</v>
+        <v>9998.50</v>
       </c>
       <c r="H85" s="17">
-        <v>0.0035381423556</v>
+        <v>0.0046977704143</v>
       </c>
       <c r="I85" s="16">
-        <v>7.72</v>
+        <v>7.21</v>
       </c>
       <c r="J85" s="11" t="s">
         <v>13</v>
@@ -3963,28 +4060,28 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D86" s="14">
-        <v>8.8</v>
+        <v>7.7541</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F86" s="15">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="G86" s="16">
-        <v>6746.18</v>
+        <v>9976.78</v>
       </c>
       <c r="H86" s="17">
-        <v>0.0033989677613</v>
+        <v>0.0046875653262</v>
       </c>
       <c r="I86" s="16">
-        <v>7.66</v>
+        <v>7.92</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>13</v>
@@ -3992,28 +4089,28 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>146</v>
       </c>
       <c r="D87" s="14">
-        <v>8.73</v>
+        <v>7.48</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c r="F87" s="15">
-        <v>6250</v>
+        <v>10000</v>
       </c>
       <c r="G87" s="16">
-        <v>6274.40</v>
+        <v>9920.76</v>
       </c>
       <c r="H87" s="17">
-        <v>0.0031612680541</v>
+        <v>0.0046612444682</v>
       </c>
       <c r="I87" s="16">
-        <v>8.50</v>
+        <v>7.82</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>13</v>
@@ -4021,28 +4118,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C88" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C88" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="D88" s="14">
-        <v>7.80</v>
+        <v>8.40</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F88" s="15">
-        <v>6250</v>
+        <v>8500</v>
       </c>
       <c r="G88" s="16">
-        <v>6259.39</v>
+        <v>8601.77</v>
       </c>
       <c r="H88" s="17">
-        <v>0.0031537054771</v>
+        <v>0.0040415202897</v>
       </c>
       <c r="I88" s="16">
-        <v>7.63</v>
+        <v>7.40</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>13</v>
@@ -4050,28 +4147,28 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>150</v>
       </c>
       <c r="D89" s="14">
-        <v>8.3</v>
+        <v>8.28</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F89" s="15">
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="G89" s="16">
-        <v>6009.06</v>
+        <v>8589.13</v>
       </c>
       <c r="H89" s="17">
-        <v>0.0030275802329</v>
+        <v>0.0040355814171</v>
       </c>
       <c r="I89" s="16">
-        <v>8.19</v>
+        <v>7.28</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
@@ -4079,28 +4176,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C90" s="13" t="s">
         <v>151</v>
       </c>
       <c r="D90" s="14">
-        <v>7.96</v>
+        <v>7.75</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F90" s="15">
-        <v>5900</v>
+        <v>800</v>
       </c>
       <c r="G90" s="16">
-        <v>5954.32</v>
+        <v>8154.11</v>
       </c>
       <c r="H90" s="17">
-        <v>0.003000000255</v>
+        <v>0.0038311883495</v>
       </c>
       <c r="I90" s="16">
-        <v>7.82</v>
+        <v>6.85</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
@@ -4108,28 +4205,28 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>152</v>
       </c>
       <c r="D91" s="14">
-        <v>5.85</v>
+        <v>7.76</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F91" s="15">
-        <v>600</v>
+        <v>8000</v>
       </c>
       <c r="G91" s="16">
-        <v>5904.67</v>
+        <v>8001.91</v>
       </c>
       <c r="H91" s="17">
-        <v>0.0029749848019</v>
+        <v>0.0037596775572</v>
       </c>
       <c r="I91" s="16">
-        <v>7.72</v>
+        <v>7.56</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
@@ -4137,28 +4234,28 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>154</v>
-      </c>
       <c r="D92" s="14">
-        <v>9.54</v>
+        <v>8.05</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F92" s="15">
-        <v>545</v>
+        <v>750</v>
       </c>
       <c r="G92" s="16">
-        <v>5790.46</v>
+        <v>7689.15</v>
       </c>
       <c r="H92" s="17">
-        <v>0.0029174417023</v>
+        <v>0.0036127280473</v>
       </c>
       <c r="I92" s="16">
-        <v>9.43</v>
+        <v>6.86</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>13</v>
@@ -4166,28 +4263,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D93" s="14">
-        <v>7.296200000000001</v>
+        <v>7.62</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F93" s="15">
-        <v>575</v>
+        <v>7500</v>
       </c>
       <c r="G93" s="16">
-        <v>5603.91</v>
+        <v>7675.01</v>
       </c>
       <c r="H93" s="17">
-        <v>0.0028234511126</v>
+        <v>0.0036060844034</v>
       </c>
       <c r="I93" s="16">
-        <v>8.39</v>
+        <v>6.61</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
@@ -4195,28 +4292,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D94" s="14">
-        <v>9.54</v>
+        <v>8.43</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F94" s="15">
-        <v>530</v>
+        <v>750</v>
       </c>
       <c r="G94" s="16">
-        <v>5597.18</v>
+        <v>7622.69</v>
       </c>
       <c r="H94" s="17">
-        <v>0.0028200602969</v>
+        <v>0.0035815019812</v>
       </c>
       <c r="I94" s="16">
-        <v>9.28</v>
+        <v>6.82</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
@@ -4224,28 +4321,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C95" s="13" t="s">
         <v>157</v>
       </c>
       <c r="D95" s="14">
-        <v>9.54</v>
+        <v>8.07</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="F95" s="15">
-        <v>530</v>
+        <v>7500</v>
       </c>
       <c r="G95" s="16">
-        <v>5591.17</v>
+        <v>7607.60</v>
       </c>
       <c r="H95" s="17">
-        <v>0.0028170322431</v>
+        <v>0.0035744119822</v>
       </c>
       <c r="I95" s="16">
-        <v>9.36</v>
+        <v>7.34</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
@@ -4253,28 +4350,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="C96" s="13" t="s">
         <v>158</v>
       </c>
       <c r="D96" s="14">
-        <v>9.54</v>
+        <v>7.21</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F96" s="15">
-        <v>530</v>
+        <v>7500</v>
       </c>
       <c r="G96" s="16">
-        <v>5557.07</v>
+        <v>7524.77</v>
       </c>
       <c r="H96" s="17">
-        <v>0.0027998514385</v>
+        <v>0.0035354945122</v>
       </c>
       <c r="I96" s="16">
-        <v>9.3</v>
+        <v>7.27</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
@@ -4282,28 +4379,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D97" s="14">
-        <v>9.54</v>
+        <v>6.59</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F97" s="15">
-        <v>530</v>
+        <v>750</v>
       </c>
       <c r="G97" s="16">
-        <v>5534.55</v>
+        <v>7493.48</v>
       </c>
       <c r="H97" s="17">
-        <v>0.0027885050537</v>
+        <v>0.0035207929834</v>
       </c>
       <c r="I97" s="16">
-        <v>9.24</v>
+        <v>6.85</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -4311,28 +4408,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>160</v>
+        <v>47</v>
       </c>
       <c r="C98" s="13" t="s">
         <v>161</v>
       </c>
       <c r="D98" s="14">
-        <v>8.45</v>
+        <v>7.90</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="F98" s="15">
-        <v>5500</v>
+        <v>700</v>
       </c>
       <c r="G98" s="16">
-        <v>5510.47</v>
+        <v>7143.82</v>
       </c>
       <c r="H98" s="17">
-        <v>0.0027763726849</v>
+        <v>0.0033565061</v>
       </c>
       <c r="I98" s="16">
-        <v>8.28</v>
+        <v>6.79</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -4340,28 +4437,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D99" s="14">
-        <v>9.54</v>
+        <v>8.8</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F99" s="15">
-        <v>530</v>
+        <v>650</v>
       </c>
       <c r="G99" s="16">
-        <v>5509.97</v>
+        <v>6878.69</v>
       </c>
       <c r="H99" s="17">
-        <v>0.0027761207669</v>
+        <v>0.0032319354274</v>
       </c>
       <c r="I99" s="16">
-        <v>9.18</v>
+        <v>6.92</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
@@ -4369,28 +4466,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C100" s="13" t="s">
         <v>164</v>
       </c>
       <c r="D100" s="14">
-        <v>8.45</v>
+        <v>8.73</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="F100" s="15">
-        <v>5500</v>
+        <v>6750</v>
       </c>
       <c r="G100" s="16">
-        <v>5507.87</v>
+        <v>6860.56</v>
       </c>
       <c r="H100" s="17">
-        <v>0.0027750627115</v>
+        <v>0.0032234170919</v>
       </c>
       <c r="I100" s="16">
-        <v>8.32</v>
+        <v>7.60</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4398,28 +4495,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C101" s="13" t="s">
         <v>165</v>
       </c>
       <c r="D101" s="14">
-        <v>7.75</v>
+        <v>7.79</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F101" s="15">
-        <v>550</v>
+        <v>6500</v>
       </c>
       <c r="G101" s="16">
-        <v>5504.28</v>
+        <v>6640.41</v>
       </c>
       <c r="H101" s="17">
-        <v>0.0027732539406</v>
+        <v>0.0031199801607</v>
       </c>
       <c r="I101" s="16">
-        <v>7.70</v>
+        <v>6.57</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4427,28 +4524,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C102" s="13" t="s">
         <v>166</v>
       </c>
       <c r="D102" s="14">
-        <v>8.45</v>
+        <v>8.73</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="F102" s="15">
-        <v>5500</v>
+        <v>6250</v>
       </c>
       <c r="G102" s="16">
-        <v>5498.53</v>
+        <v>6376.14</v>
       </c>
       <c r="H102" s="17">
-        <v>0.0027703568841</v>
+        <v>0.002995813557</v>
       </c>
       <c r="I102" s="16">
-        <v>8.38</v>
+        <v>7.61</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4456,28 +4553,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C103" s="13" t="s">
         <v>167</v>
       </c>
       <c r="D103" s="14">
-        <v>8.45</v>
+        <v>7.22</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="F103" s="15">
-        <v>5500</v>
+        <v>6300</v>
       </c>
       <c r="G103" s="16">
-        <v>5492.75</v>
+        <v>6324.61</v>
       </c>
       <c r="H103" s="17">
-        <v>0.0027674447125</v>
+        <v>0.0029716023143</v>
       </c>
       <c r="I103" s="16">
-        <v>8.43</v>
+        <v>7.26</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
@@ -4485,28 +4582,28 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
       <c r="B104" s="12" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D104" s="14">
-        <v>9.54</v>
+        <v>7.80</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F104" s="15">
-        <v>530</v>
+        <v>6250</v>
       </c>
       <c r="G104" s="16">
-        <v>5483.16</v>
+        <v>6322.57</v>
       </c>
       <c r="H104" s="17">
-        <v>0.0027626129261</v>
+        <v>0.0029706438254</v>
       </c>
       <c r="I104" s="16">
-        <v>9.12</v>
+        <v>6.56</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4514,28 +4611,28 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D105" s="14">
-        <v>9.54</v>
+        <v>7.96</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F105" s="15">
-        <v>530</v>
+        <v>5900</v>
       </c>
       <c r="G105" s="16">
-        <v>5453.98</v>
+        <v>6072.99</v>
       </c>
       <c r="H105" s="17">
-        <v>0.0027479109942</v>
+        <v>0.0028533792817</v>
       </c>
       <c r="I105" s="16">
-        <v>9.04</v>
+        <v>6.89</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
@@ -4543,28 +4640,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D106" s="14">
-        <v>9.54</v>
+        <v>6.23</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F106" s="15">
-        <v>515</v>
+        <v>600</v>
       </c>
       <c r="G106" s="16">
-        <v>5418.88</v>
+        <v>5969.17</v>
       </c>
       <c r="H106" s="17">
-        <v>0.0027302263536</v>
+        <v>0.0028045997123</v>
       </c>
       <c r="I106" s="16">
-        <v>9.45</v>
+        <v>6.59</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4572,28 +4669,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D107" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F107" s="15">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="G107" s="16">
-        <v>5318.27</v>
+        <v>5773.56</v>
       </c>
       <c r="H107" s="17">
-        <v>0.0026795354224</v>
+        <v>0.0027126928392</v>
       </c>
       <c r="I107" s="16">
-        <v>9.47</v>
+        <v>8.93</v>
       </c>
       <c r="J107" s="11" t="s">
         <v>13</v>
@@ -4601,28 +4698,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="12" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D108" s="14">
-        <v>8.32</v>
+        <v>7.296200000000001</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F108" s="15">
-        <v>5200</v>
+        <v>575</v>
       </c>
       <c r="G108" s="16">
-        <v>5240.6</v>
+        <v>5672.31</v>
       </c>
       <c r="H108" s="17">
-        <v>0.002640402487</v>
+        <v>0.002665120778</v>
       </c>
       <c r="I108" s="16">
-        <v>8.02</v>
+        <v>7.98</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4630,28 +4727,28 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D109" s="14">
-        <v>7.61</v>
+        <v>9.58</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F109" s="15">
-        <v>5000</v>
+        <v>530</v>
       </c>
       <c r="G109" s="16">
-        <v>5033.28</v>
+        <v>5605.69</v>
       </c>
       <c r="H109" s="17">
-        <v>0.0025359472254</v>
+        <v>0.0026338195363</v>
       </c>
       <c r="I109" s="16">
-        <v>7.50</v>
+        <v>8.63</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>13</v>
@@ -4659,28 +4756,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D110" s="14">
-        <v>7.55</v>
+        <v>9.58</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F110" s="15">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="G110" s="16">
-        <v>5005.94</v>
+        <v>5597.79</v>
       </c>
       <c r="H110" s="17">
-        <v>0.0025221723516</v>
+        <v>0.0026301077409</v>
       </c>
       <c r="I110" s="16">
-        <v>7.49</v>
+        <v>8.81</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>13</v>
@@ -4688,28 +4785,28 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D111" s="14">
-        <v>9.3</v>
+        <v>9.58</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="F111" s="15">
-        <v>5000</v>
+        <v>530</v>
       </c>
       <c r="G111" s="16">
-        <v>4999.31</v>
+        <v>5576.99</v>
       </c>
       <c r="H111" s="17">
-        <v>0.0025188319195</v>
+        <v>0.0026203349125</v>
       </c>
       <c r="I111" s="16">
-        <v>9.29</v>
+        <v>8.25</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>13</v>
@@ -4717,28 +4814,28 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
       <c r="B112" s="12" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D112" s="14">
-        <v>7.640000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F112" s="15">
-        <v>5000</v>
+        <v>530</v>
       </c>
       <c r="G112" s="16">
-        <v>4997.57</v>
+        <v>5575.68</v>
       </c>
       <c r="H112" s="17">
-        <v>0.002517955245</v>
+        <v>0.0026197194123</v>
       </c>
       <c r="I112" s="16">
-        <v>7.63</v>
+        <v>7.06</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>13</v>
@@ -4746,28 +4843,28 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D113" s="14">
-        <v>7.49</v>
+        <v>9.58</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F113" s="15">
-        <v>5000</v>
+        <v>530</v>
       </c>
       <c r="G113" s="16">
-        <v>4987.75</v>
+        <v>5575.24</v>
       </c>
       <c r="H113" s="17">
-        <v>0.0025130075763</v>
+        <v>0.0026195126793</v>
       </c>
       <c r="I113" s="16">
-        <v>7.61</v>
+        <v>7.64</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>13</v>
@@ -4775,28 +4872,28 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
       <c r="B114" s="12" t="s">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D114" s="14">
-        <v>6.50</v>
+        <v>9.58</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F114" s="15">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="G114" s="16">
-        <v>4915.84</v>
+        <v>5574.66</v>
       </c>
       <c r="H114" s="17">
-        <v>0.0024767767358</v>
+        <v>0.0026192401678</v>
       </c>
       <c r="I114" s="16">
-        <v>7.80</v>
+        <v>8.47</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>13</v>
@@ -4804,28 +4901,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D115" s="14">
-        <v>7.750500000000001</v>
+        <v>8.45</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="F115" s="15">
-        <v>400</v>
+        <v>5500</v>
       </c>
       <c r="G115" s="16">
-        <v>3976.27</v>
+        <v>5571.97</v>
       </c>
       <c r="H115" s="17">
-        <v>0.0020033876268</v>
+        <v>0.002617976278</v>
       </c>
       <c r="I115" s="16">
-        <v>8.45</v>
+        <v>7.34</v>
       </c>
       <c r="J115" s="11" t="s">
         <v>13</v>
@@ -4833,28 +4930,28 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
       <c r="B116" s="12" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D116" s="14">
-        <v>6.75</v>
+        <v>9.58</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>182</v>
+        <v>49</v>
       </c>
       <c r="F116" s="15">
-        <v>400</v>
+        <v>530</v>
       </c>
       <c r="G116" s="16">
-        <v>3940.38</v>
+        <v>5568.68</v>
       </c>
       <c r="H116" s="17">
-        <v>0.0019853049558</v>
+        <v>0.0026164304796</v>
       </c>
       <c r="I116" s="16">
-        <v>8.66</v>
+        <v>8.01</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
@@ -4862,28 +4959,28 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="12" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D117" s="14">
-        <v>8.73</v>
+        <v>8.45</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F117" s="15">
-        <v>3750</v>
+        <v>5500</v>
       </c>
       <c r="G117" s="16">
-        <v>3762.18</v>
+        <v>5546.54</v>
       </c>
       <c r="H117" s="17">
-        <v>0.0018955213961</v>
+        <v>0.0026060280556</v>
       </c>
       <c r="I117" s="16">
-        <v>8.53</v>
+        <v>7.39</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
@@ -4891,28 +4988,28 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
       <c r="B118" s="12" t="s">
-        <v>56</v>
+        <v>181</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D118" s="14">
-        <v>7.96</v>
+        <v>8.45</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="F118" s="15">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="G118" s="16">
-        <v>3519.25</v>
+        <v>5513.94</v>
       </c>
       <c r="H118" s="17">
-        <v>0.0017731245377</v>
+        <v>0.0025907110265</v>
       </c>
       <c r="I118" s="16">
-        <v>7.87</v>
+        <v>7.30</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>13</v>
@@ -4920,28 +5017,28 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D119" s="14">
-        <v>8.35</v>
+        <v>9.58</v>
       </c>
       <c r="E119" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F119" s="15">
-        <v>3500</v>
+        <v>515</v>
       </c>
       <c r="G119" s="16">
-        <v>3505.30</v>
+        <v>5444.88</v>
       </c>
       <c r="H119" s="17">
-        <v>0.0017660960267</v>
+        <v>0.0025582633568</v>
       </c>
       <c r="I119" s="16">
-        <v>8.19</v>
+        <v>8.83</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>13</v>
@@ -4949,28 +5046,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D120" s="14">
-        <v>7.56</v>
+        <v>8.32</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F120" s="15">
-        <v>3500</v>
+        <v>5200</v>
       </c>
       <c r="G120" s="16">
-        <v>3504.03</v>
+        <v>5339.15</v>
       </c>
       <c r="H120" s="17">
-        <v>0.0017654561551</v>
+        <v>0.0025085863787</v>
       </c>
       <c r="I120" s="16">
-        <v>7.48</v>
+        <v>7.19</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>13</v>
@@ -4978,28 +5075,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D121" s="14">
-        <v>7.96</v>
+        <v>9.58</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F121" s="15">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G121" s="16">
-        <v>3016.77</v>
+        <v>5322.59</v>
       </c>
       <c r="H121" s="17">
-        <v>0.001519957068</v>
+        <v>0.0025008057038</v>
       </c>
       <c r="I121" s="16">
-        <v>7.95</v>
+        <v>8.95</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>13</v>
@@ -5007,28 +5104,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D122" s="14">
-        <v>7.45</v>
+        <v>7.61</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F122" s="15">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="G122" s="16">
-        <v>2966.96</v>
+        <v>5152.72</v>
       </c>
       <c r="H122" s="17">
-        <v>0.0014948610012</v>
+        <v>0.0024209927058</v>
       </c>
       <c r="I122" s="16">
-        <v>8.03</v>
+        <v>7.14</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>13</v>
@@ -5039,25 +5136,25 @@
         <v>50</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D123" s="14">
-        <v>7.95</v>
+        <v>7.48</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F123" s="15">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="G123" s="16">
-        <v>2510.78</v>
+        <v>5127.89</v>
       </c>
       <c r="H123" s="17">
-        <v>0.0012650211342</v>
+        <v>0.0024093263919</v>
       </c>
       <c r="I123" s="16">
-        <v>7.71</v>
+        <v>6.60</v>
       </c>
       <c r="J123" s="11" t="s">
         <v>13</v>
@@ -5065,28 +5162,28 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
       <c r="B124" s="12" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D124" s="14">
-        <v>7.62</v>
+        <v>7.55</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F124" s="15">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="G124" s="16">
-        <v>2507.06</v>
+        <v>5124.03</v>
       </c>
       <c r="H124" s="17">
-        <v>0.0012631468647</v>
+        <v>0.0024075127805</v>
       </c>
       <c r="I124" s="16">
-        <v>7.50</v>
+        <v>6.55</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>13</v>
@@ -5094,28 +5191,28 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C125" s="13" t="s">
         <v>192</v>
       </c>
       <c r="D125" s="14">
-        <v>7.77</v>
+        <v>7.640000000000001</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F125" s="15">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="G125" s="16">
-        <v>2505.7</v>
+        <v>5053.93</v>
       </c>
       <c r="H125" s="17">
-        <v>0.0012624616478</v>
+        <v>0.0023745764694</v>
       </c>
       <c r="I125" s="16">
-        <v>7.62</v>
+        <v>6.56</v>
       </c>
       <c r="J125" s="11" t="s">
         <v>13</v>
@@ -5123,28 +5220,28 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C126" s="13" t="s">
         <v>193</v>
       </c>
       <c r="D126" s="14">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F126" s="15">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="G126" s="16">
-        <v>2503.17</v>
+        <v>5052.21</v>
       </c>
       <c r="H126" s="17">
-        <v>0.0012611869429</v>
+        <v>0.0023737683317</v>
       </c>
       <c r="I126" s="16">
-        <v>7.47</v>
+        <v>6.63</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>13</v>
@@ -5152,28 +5249,28 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
       <c r="B127" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C127" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="C127" s="13" t="s">
-        <v>195</v>
-      </c>
       <c r="D127" s="14">
-        <v>7.86</v>
+        <v>8.3</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F127" s="15">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="G127" s="16">
-        <v>2502.71</v>
+        <v>5048.99</v>
       </c>
       <c r="H127" s="17">
-        <v>0.0012609551784</v>
+        <v>0.0023722554227</v>
       </c>
       <c r="I127" s="16">
-        <v>7.96</v>
+        <v>7.28</v>
       </c>
       <c r="J127" s="11" t="s">
         <v>13</v>
@@ -5181,28 +5278,28 @@
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
       <c r="B128" s="12" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D128" s="14">
-        <v>7.83</v>
+        <v>7.27</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F128" s="15">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="G128" s="16">
-        <v>2501.16</v>
+        <v>5021.1</v>
       </c>
       <c r="H128" s="17">
-        <v>0.0012601742328</v>
+        <v>0.0023591513754</v>
       </c>
       <c r="I128" s="16">
-        <v>7.76</v>
+        <v>7.03</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>13</v>
@@ -5210,28 +5307,28 @@
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
       <c r="B129" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C129" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C129" s="13" t="s">
-        <v>198</v>
-      </c>
       <c r="D129" s="14">
-        <v>7.10</v>
+        <v>9.3</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="F129" s="15">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="G129" s="16">
-        <v>2499.25</v>
+        <v>5020.93</v>
       </c>
       <c r="H129" s="17">
-        <v>0.0012592119062</v>
+        <v>0.0023590715013</v>
       </c>
       <c r="I129" s="16">
-        <v>7.30</v>
+        <v>8.50</v>
       </c>
       <c r="J129" s="11" t="s">
         <v>13</v>
@@ -5239,28 +5336,28 @@
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1">
       <c r="B130" s="12" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D130" s="14">
-        <v>7.55</v>
+        <v>6.50</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F130" s="15">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="G130" s="16">
-        <v>2497.62</v>
+        <v>4979.23</v>
       </c>
       <c r="H130" s="17">
-        <v>0.0012583906536</v>
+        <v>0.0023394788598</v>
       </c>
       <c r="I130" s="16">
-        <v>7.62</v>
+        <v>6.92</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>13</v>
@@ -5268,28 +5365,28 @@
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1">
       <c r="B131" s="12" t="s">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D131" s="14">
-        <v>7.69</v>
+        <v>7.750500000000001</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F131" s="15">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="G131" s="16">
-        <v>2496.45</v>
+        <v>3991.82</v>
       </c>
       <c r="H131" s="17">
-        <v>0.0012578011656</v>
+        <v>0.0018755467215</v>
       </c>
       <c r="I131" s="16">
-        <v>7.76</v>
+        <v>7.92</v>
       </c>
       <c r="J131" s="11" t="s">
         <v>13</v>
@@ -5297,28 +5394,28 @@
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1">
       <c r="B132" s="12" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="C132" s="13" t="s">
         <v>201</v>
       </c>
       <c r="D132" s="14">
-        <v>7.56</v>
+        <v>6.75</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>40</v>
+        <v>202</v>
       </c>
       <c r="F132" s="15">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="G132" s="16">
-        <v>2496.23</v>
+        <v>3982.76</v>
       </c>
       <c r="H132" s="17">
-        <v>0.0012576903217</v>
+        <v>0.001871289903</v>
       </c>
       <c r="I132" s="16">
-        <v>7.63</v>
+        <v>7.46</v>
       </c>
       <c r="J132" s="11" t="s">
         <v>13</v>
@@ -5326,28 +5423,28 @@
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1">
       <c r="B133" s="12" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D133" s="14">
-        <v>7.13</v>
+        <v>7.59</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F133" s="15">
-        <v>250</v>
+        <v>3750</v>
       </c>
       <c r="G133" s="16">
-        <v>2488.66</v>
+        <v>3822.92</v>
       </c>
       <c r="H133" s="17">
-        <v>0.0012538762838</v>
+        <v>0.0017961894756</v>
       </c>
       <c r="I133" s="16">
-        <v>7.78</v>
+        <v>6.52</v>
       </c>
       <c r="J133" s="11" t="s">
         <v>13</v>
@@ -5355,28 +5452,28 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
       <c r="B134" s="12" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D134" s="14">
-        <v>7.7475</v>
+        <v>7.56</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F134" s="15">
-        <v>250</v>
+        <v>3500</v>
       </c>
       <c r="G134" s="16">
-        <v>2486.40</v>
+        <v>3571.65</v>
       </c>
       <c r="H134" s="17">
-        <v>0.0012527376147</v>
+        <v>0.0016781308896</v>
       </c>
       <c r="I134" s="16">
-        <v>8.45</v>
+        <v>6.53</v>
       </c>
       <c r="J134" s="11" t="s">
         <v>13</v>
@@ -5384,28 +5481,28 @@
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1">
       <c r="B135" s="12" t="s">
-        <v>204</v>
+        <v>67</v>
       </c>
       <c r="C135" s="13" t="s">
         <v>205</v>
       </c>
       <c r="D135" s="14">
-        <v>5.78</v>
+        <v>7.96</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F135" s="15">
-        <v>250</v>
+        <v>3500</v>
       </c>
       <c r="G135" s="16">
-        <v>2474.62</v>
+        <v>3566.09</v>
       </c>
       <c r="H135" s="17">
-        <v>0.0012468024276</v>
+        <v>0.0016755185374</v>
       </c>
       <c r="I135" s="16">
-        <v>7.85</v>
+        <v>6.84</v>
       </c>
       <c r="J135" s="11" t="s">
         <v>13</v>
@@ -5413,28 +5510,28 @@
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1">
       <c r="B136" s="12" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C136" s="13" t="s">
         <v>206</v>
       </c>
       <c r="D136" s="14">
-        <v>9.40</v>
+        <v>7.75</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="F136" s="15">
-        <v>213</v>
+        <v>3000</v>
       </c>
       <c r="G136" s="16">
-        <v>2153.2</v>
+        <v>3065.01</v>
       </c>
       <c r="H136" s="17">
-        <v>0.0010848594884</v>
+        <v>0.0014400873428</v>
       </c>
       <c r="I136" s="16">
-        <v>8.55</v>
+        <v>6.57</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>13</v>
@@ -5442,28 +5539,28 @@
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1">
       <c r="B137" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C137" s="13" t="s">
         <v>207</v>
       </c>
       <c r="D137" s="14">
-        <v>8.32</v>
+        <v>7.96</v>
       </c>
       <c r="E137" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F137" s="15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G137" s="16">
-        <v>2022.11</v>
+        <v>3060.61</v>
       </c>
       <c r="H137" s="17">
-        <v>0.0010188116385</v>
+        <v>0.0014380200137</v>
       </c>
       <c r="I137" s="16">
-        <v>7.99</v>
+        <v>7.20</v>
       </c>
       <c r="J137" s="11" t="s">
         <v>13</v>
@@ -5471,28 +5568,28 @@
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1">
       <c r="B138" s="12" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D138" s="14">
-        <v>7.3029</v>
+        <v>7.2503</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F138" s="15">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="G138" s="16">
-        <v>1953.25</v>
+        <v>3024.16</v>
       </c>
       <c r="H138" s="17">
-        <v>0.0009841174975</v>
+        <v>0.0014208940717</v>
       </c>
       <c r="I138" s="16">
-        <v>8.38</v>
+        <v>7.13</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>13</v>
@@ -5500,28 +5597,28 @@
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1">
       <c r="B139" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D139" s="14">
+        <v>7.45</v>
+      </c>
+      <c r="E139" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C139" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D139" s="14">
-        <v>8.90</v>
-      </c>
-      <c r="E139" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="F139" s="15">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="G139" s="16">
-        <v>1504.58</v>
+        <v>3017.34</v>
       </c>
       <c r="H139" s="17">
-        <v>0.0007580614383</v>
+        <v>0.0014176897116</v>
       </c>
       <c r="I139" s="16">
-        <v>8.39</v>
+        <v>7.07</v>
       </c>
       <c r="J139" s="11" t="s">
         <v>13</v>
@@ -5529,28 +5626,28 @@
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
       <c r="B140" s="12" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D140" s="14">
-        <v>8.03</v>
+        <v>7.74</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F140" s="15">
-        <v>125</v>
+        <v>2500</v>
       </c>
       <c r="G140" s="16">
-        <v>1254.91</v>
+        <v>2546.59</v>
       </c>
       <c r="H140" s="17">
-        <v>0.0006322687259</v>
+        <v>0.0011965089922</v>
       </c>
       <c r="I140" s="16">
-        <v>7.64</v>
+        <v>6.85</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>13</v>
@@ -5558,28 +5655,28 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1">
       <c r="B141" s="12" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="C141" s="13" t="s">
         <v>212</v>
       </c>
       <c r="D141" s="14">
-        <v>8.56</v>
+        <v>7.71</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F141" s="15">
-        <v>120</v>
+        <v>2500</v>
       </c>
       <c r="G141" s="16">
-        <v>1247.04</v>
+        <v>2546.36</v>
       </c>
       <c r="H141" s="17">
-        <v>0.0006283035372</v>
+        <v>0.0011964009273</v>
       </c>
       <c r="I141" s="16">
-        <v>7.50</v>
+        <v>6.52</v>
       </c>
       <c r="J141" s="11" t="s">
         <v>13</v>
@@ -5587,28 +5684,28 @@
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1">
       <c r="B142" s="12" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C142" s="13" t="s">
         <v>213</v>
       </c>
       <c r="D142" s="14">
-        <v>8.50</v>
+        <v>7.95</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F142" s="15">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="G142" s="16">
-        <v>208.40</v>
+        <v>2544.78</v>
       </c>
       <c r="H142" s="17">
-        <v>0.0001049994043</v>
+        <v>0.0011956585682</v>
       </c>
       <c r="I142" s="16">
-        <v>7.42</v>
+        <v>6.85</v>
       </c>
       <c r="J142" s="11" t="s">
         <v>13</v>
@@ -5616,36 +5713,57 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1">
       <c r="B143" s="12" t="s">
-        <v>13</v>
+        <v>82</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="D143" s="14">
+        <v>7.77</v>
+      </c>
+      <c r="E143" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F143" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G143" s="16">
+        <v>2532.19</v>
+      </c>
+      <c r="H143" s="17">
+        <v>0.001189743188</v>
+      </c>
+      <c r="I143" s="16">
+        <v>6.55</v>
       </c>
       <c r="J143" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1">
-      <c r="B144" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G144" s="9">
-        <v>12214.85</v>
-      </c>
-      <c r="H144" s="10">
-        <v>0.006154280105</v>
-      </c>
-      <c r="I144" s="9" t="s">
-        <v>13</v>
+      <c r="B144" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D144" s="14">
+        <v>7.70</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F144" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G144" s="16">
+        <v>2531.52</v>
+      </c>
+      <c r="H144" s="17">
+        <v>0.0011894283901</v>
+      </c>
+      <c r="I144" s="16">
+        <v>6.55</v>
       </c>
       <c r="J144" s="11" t="s">
         <v>13</v>
@@ -5653,28 +5771,28 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1">
       <c r="B145" s="12" t="s">
-        <v>215</v>
+        <v>47</v>
       </c>
       <c r="C145" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>13</v>
+      <c r="D145" s="14">
+        <v>7.83</v>
       </c>
       <c r="E145" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F145" s="15">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="G145" s="16">
-        <v>12214.85</v>
+        <v>2529.44</v>
       </c>
       <c r="H145" s="17">
-        <v>0.006154280105</v>
+        <v>0.0011884511073</v>
       </c>
       <c r="I145" s="16">
-        <v>8.11</v>
+        <v>6.82</v>
       </c>
       <c r="J145" s="11" t="s">
         <v>13</v>
@@ -5682,36 +5800,57 @@
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1">
       <c r="B146" s="12" t="s">
-        <v>13</v>
+        <v>47</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D146" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F146" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G146" s="16">
+        <v>2529.04</v>
+      </c>
+      <c r="H146" s="17">
+        <v>0.0011882631683</v>
+      </c>
+      <c r="I146" s="16">
+        <v>6.82</v>
       </c>
       <c r="J146" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="147" spans="2:10" ht="15" customHeight="1">
-      <c r="B147" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G147" s="9" t="s">
+      <c r="B147" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C147" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="H147" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I147" s="9" t="s">
-        <v>13</v>
+      <c r="D147" s="14">
+        <v>7.55</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F147" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G147" s="16">
+        <v>2526.59</v>
+      </c>
+      <c r="H147" s="17">
+        <v>0.0011871120419</v>
+      </c>
+      <c r="I147" s="16">
+        <v>6.55</v>
       </c>
       <c r="J147" s="11" t="s">
         <v>13</v>
@@ -5719,36 +5858,57 @@
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1">
       <c r="B148" s="12" t="s">
-        <v>13</v>
+        <v>168</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D148" s="14">
+        <v>7.56</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F148" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G148" s="16">
+        <v>2524.95</v>
+      </c>
+      <c r="H148" s="17">
+        <v>0.0011863414919</v>
+      </c>
+      <c r="I148" s="16">
+        <v>6.56</v>
       </c>
       <c r="J148" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="149" spans="2:10" ht="15" customHeight="1">
-      <c r="B149" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D149" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F149" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G149" s="9">
-        <v>114230.82</v>
-      </c>
-      <c r="H149" s="10">
-        <v>0.05755358951689999</v>
-      </c>
-      <c r="I149" s="9" t="s">
-        <v>13</v>
+      <c r="B149" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D149" s="14">
+        <v>7.86</v>
+      </c>
+      <c r="E149" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F149" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G149" s="16">
+        <v>2515.10</v>
+      </c>
+      <c r="H149" s="17">
+        <v>0.0011817134939</v>
+      </c>
+      <c r="I149" s="16">
+        <v>6.89</v>
       </c>
       <c r="J149" s="11" t="s">
         <v>13</v>
@@ -5756,28 +5916,28 @@
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1">
       <c r="B150" s="12" t="s">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="C150" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="D150" s="13" t="s">
-        <v>13</v>
+      <c r="D150" s="14">
+        <v>7.7475</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="F150" s="15">
-        <v>3500000000</v>
+        <v>250</v>
       </c>
       <c r="G150" s="16">
-        <v>35070</v>
+        <v>2495.61</v>
       </c>
       <c r="H150" s="17">
-        <v>0.017669525478</v>
+        <v>0.0011725561658</v>
       </c>
       <c r="I150" s="16">
-        <v>9.21</v>
+        <v>7.92</v>
       </c>
       <c r="J150" s="11" t="s">
         <v>13</v>
@@ -5785,28 +5945,28 @@
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1">
       <c r="B151" s="12" t="s">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>13</v>
+        <v>222</v>
+      </c>
+      <c r="D151" s="14">
+        <v>9.40</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="F151" s="15">
-        <v>2000000000</v>
+        <v>213</v>
       </c>
       <c r="G151" s="16">
-        <v>18730</v>
+        <v>2158.02</v>
       </c>
       <c r="H151" s="17">
-        <v>0.0094368466553</v>
+        <v>0.001013940342</v>
       </c>
       <c r="I151" s="16">
-        <v>9.21</v>
+        <v>8.01</v>
       </c>
       <c r="J151" s="11" t="s">
         <v>13</v>
@@ -5814,28 +5974,28 @@
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1">
       <c r="B152" s="12" t="s">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>13</v>
+        <v>223</v>
+      </c>
+      <c r="D152" s="14">
+        <v>8.32</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>227</v>
+        <v>63</v>
       </c>
       <c r="F152" s="15">
-        <v>145</v>
+        <v>2000</v>
       </c>
       <c r="G152" s="16">
-        <v>14280.65</v>
+        <v>2066.40</v>
       </c>
       <c r="H152" s="17">
-        <v>0.0071951043347</v>
+        <v>0.0009708929123</v>
       </c>
       <c r="I152" s="16">
-        <v>8.32</v>
+        <v>7.26</v>
       </c>
       <c r="J152" s="11" t="s">
         <v>13</v>
@@ -5843,28 +6003,28 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1">
       <c r="B153" s="12" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D153" s="13" t="s">
-        <v>13</v>
+        <v>224</v>
+      </c>
+      <c r="D153" s="14">
+        <v>7.3029</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>227</v>
+        <v>63</v>
       </c>
       <c r="F153" s="15">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="G153" s="16">
-        <v>10895.50</v>
+        <v>1974.92</v>
       </c>
       <c r="H153" s="17">
-        <v>0.0054895441929</v>
+        <v>0.0009279112613</v>
       </c>
       <c r="I153" s="16">
-        <v>8.34</v>
+        <v>7.98</v>
       </c>
       <c r="J153" s="11" t="s">
         <v>13</v>
@@ -5872,28 +6032,28 @@
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1">
       <c r="B154" s="12" t="s">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>13</v>
+        <v>225</v>
+      </c>
+      <c r="D154" s="14">
+        <v>7.68</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="F154" s="15">
-        <v>109</v>
+        <v>1500</v>
       </c>
       <c r="G154" s="16">
-        <v>9850.57</v>
+        <v>1532.96</v>
       </c>
       <c r="H154" s="17">
-        <v>0.004963070932</v>
+        <v>0.000720257452</v>
       </c>
       <c r="I154" s="16">
-        <v>8.35</v>
+        <v>6.58</v>
       </c>
       <c r="J154" s="11" t="s">
         <v>13</v>
@@ -5901,28 +6061,28 @@
     </row>
     <row r="155" spans="2:10" ht="15" customHeight="1">
       <c r="B155" s="12" t="s">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D155" s="13" t="s">
-        <v>13</v>
+        <v>226</v>
+      </c>
+      <c r="D155" s="14">
+        <v>8.90</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="F155" s="15">
-        <v>94</v>
+        <v>1500</v>
       </c>
       <c r="G155" s="16">
-        <v>9371.65</v>
+        <v>1507.32</v>
       </c>
       <c r="H155" s="17">
-        <v>0.0047217738365</v>
+        <v>0.0007082105616</v>
       </c>
       <c r="I155" s="16">
-        <v>8.41</v>
+        <v>7.58</v>
       </c>
       <c r="J155" s="11" t="s">
         <v>13</v>
@@ -5930,28 +6090,28 @@
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1">
       <c r="B156" s="12" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>13</v>
+        <v>227</v>
+      </c>
+      <c r="D156" s="14">
+        <v>7.95</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="F156" s="15">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="G156" s="16">
-        <v>9337.27</v>
+        <v>1278.81</v>
       </c>
       <c r="H156" s="17">
-        <v>0.0047044519578</v>
+        <v>0.0006008457052</v>
       </c>
       <c r="I156" s="16">
-        <v>8.41</v>
+        <v>6.52</v>
       </c>
       <c r="J156" s="11" t="s">
         <v>13</v>
@@ -5959,28 +6119,28 @@
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1">
       <c r="B157" s="12" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D157" s="13" t="s">
-        <v>13</v>
+        <v>228</v>
+      </c>
+      <c r="D157" s="14">
+        <v>8.56</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>227</v>
+        <v>49</v>
       </c>
       <c r="F157" s="15">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="G157" s="16">
-        <v>6695.18</v>
+        <v>1278.33</v>
       </c>
       <c r="H157" s="17">
-        <v>0.0033732721297</v>
+        <v>0.0006006201784</v>
       </c>
       <c r="I157" s="16">
-        <v>8.34</v>
+        <v>6.55</v>
       </c>
       <c r="J157" s="11" t="s">
         <v>13</v>
@@ -5988,36 +6148,57 @@
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1">
       <c r="B158" s="12" t="s">
-        <v>13</v>
+        <v>59</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D158" s="14">
+        <v>8.03</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F158" s="15">
+        <v>125</v>
+      </c>
+      <c r="G158" s="16">
+        <v>1265.55</v>
+      </c>
+      <c r="H158" s="17">
+        <v>0.0005946155271</v>
+      </c>
+      <c r="I158" s="16">
+        <v>6.55</v>
       </c>
       <c r="J158" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1">
-      <c r="B159" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D159" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G159" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I159" s="9" t="s">
-        <v>13</v>
+      <c r="B159" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="D159" s="14">
+        <v>7.68</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F159" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G159" s="16">
+        <v>1022.79</v>
+      </c>
+      <c r="H159" s="17">
+        <v>0.0004805553435</v>
+      </c>
+      <c r="I159" s="16">
+        <v>6.58</v>
       </c>
       <c r="J159" s="11" t="s">
         <v>13</v>
@@ -6025,36 +6206,57 @@
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1">
       <c r="B160" s="12" t="s">
-        <v>13</v>
+        <v>52</v>
+      </c>
+      <c r="C160" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D160" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="E160" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F160" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G160" s="16">
+        <v>1019.70</v>
+      </c>
+      <c r="H160" s="17">
+        <v>0.0004791035146</v>
+      </c>
+      <c r="I160" s="16">
+        <v>6.61</v>
       </c>
       <c r="J160" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1">
-      <c r="B161" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G161" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I161" s="9" t="s">
-        <v>13</v>
+      <c r="B161" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D161" s="14">
+        <v>8.97</v>
+      </c>
+      <c r="E161" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F161" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G161" s="16">
+        <v>1012.99</v>
+      </c>
+      <c r="H161" s="17">
+        <v>0.0004759508378</v>
+      </c>
+      <c r="I161" s="16">
+        <v>8.04</v>
       </c>
       <c r="J161" s="11" t="s">
         <v>13</v>
@@ -6062,73 +6264,94 @@
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1">
       <c r="B162" s="12" t="s">
-        <v>13</v>
+        <v>52</v>
+      </c>
+      <c r="C162" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D162" s="14">
+        <v>8.50</v>
+      </c>
+      <c r="E162" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F162" s="15">
+        <v>20</v>
+      </c>
+      <c r="G162" s="16">
+        <v>212.71</v>
+      </c>
+      <c r="H162" s="17">
+        <v>0.0000999412656</v>
+      </c>
+      <c r="I162" s="16">
+        <v>6.66</v>
       </c>
       <c r="J162" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1">
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" ht="15" customHeight="1">
+      <c r="B164" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="9">
+        <v>12658.17</v>
+      </c>
+      <c r="H164" s="10">
+        <v>0.005947409764</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J164" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" ht="15" customHeight="1">
+      <c r="B165" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C165" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C163" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G163" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J163" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="164" spans="2:10" ht="15" customHeight="1">
-      <c r="B164" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J164" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="165" spans="2:10" ht="15" customHeight="1">
-      <c r="B165" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D165" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E165" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F165" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G165" s="9">
-        <v>14853.90</v>
-      </c>
-      <c r="H165" s="10">
-        <v>0.0074839282718</v>
-      </c>
-      <c r="I165" s="9" t="s">
-        <v>13</v>
+      <c r="D165" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E165" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F165" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G165" s="16">
+        <v>12658.17</v>
+      </c>
+      <c r="H165" s="17">
+        <v>0.005947409764</v>
+      </c>
+      <c r="I165" s="16">
+        <v>7.24</v>
       </c>
       <c r="J165" s="11" t="s">
         <v>13</v>
@@ -6144,25 +6367,25 @@
     </row>
     <row r="167" spans="2:10" ht="15" customHeight="1">
       <c r="B167" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C167" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G167" s="9">
-        <v>14853.90</v>
-      </c>
-      <c r="H167" s="10">
-        <v>0.0074839282718</v>
+      <c r="H167" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="I167" s="9" t="s">
         <v>13</v>
@@ -6173,57 +6396,36 @@
     </row>
     <row r="168" spans="2:10" ht="15" customHeight="1">
       <c r="B168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J168" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" ht="15" customHeight="1">
+      <c r="B169" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C168" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E168" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F168" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G168" s="16">
-        <v>9878.22</v>
-      </c>
-      <c r="H168" s="17">
-        <v>0.004977001995</v>
-      </c>
-      <c r="I168" s="16">
-        <v>7.50</v>
-      </c>
-      <c r="J168" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="169" spans="2:10" ht="15" customHeight="1">
-      <c r="B169" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="C169" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="D169" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E169" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F169" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G169" s="16">
-        <v>4975.68</v>
-      </c>
-      <c r="H169" s="17">
-        <v>0.0025069262768</v>
-      </c>
-      <c r="I169" s="16">
-        <v>7.14</v>
+      <c r="C169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="9">
+        <v>100316.22</v>
+      </c>
+      <c r="H169" s="10">
+        <v>0.0471333270382</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J169" s="11" t="s">
         <v>13</v>
@@ -6231,36 +6433,57 @@
     </row>
     <row r="170" spans="2:10" ht="15" customHeight="1">
       <c r="B170" s="12" t="s">
-        <v>13</v>
+        <v>240</v>
+      </c>
+      <c r="C170" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F170" s="15">
+        <v>3500000000</v>
+      </c>
+      <c r="G170" s="16">
+        <v>31608.50</v>
+      </c>
+      <c r="H170" s="17">
+        <v>0.0148511752904</v>
+      </c>
+      <c r="I170" s="16">
+        <v>8.60</v>
       </c>
       <c r="J170" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="171" spans="2:10" ht="15" customHeight="1">
-      <c r="B171" s="7" t="s">
+      <c r="B171" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C171" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G171" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I171" s="9" t="s">
-        <v>13</v>
+      <c r="D171" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F171" s="15">
+        <v>2000000000</v>
+      </c>
+      <c r="G171" s="16">
+        <v>14176</v>
+      </c>
+      <c r="H171" s="17">
+        <v>0.0066605584231</v>
+      </c>
+      <c r="I171" s="16">
+        <v>8.58</v>
       </c>
       <c r="J171" s="11" t="s">
         <v>13</v>
@@ -6268,36 +6491,57 @@
     </row>
     <row r="172" spans="2:10" ht="15" customHeight="1">
       <c r="B172" s="12" t="s">
-        <v>13</v>
+        <v>245</v>
+      </c>
+      <c r="C172" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F172" s="15">
+        <v>145</v>
+      </c>
+      <c r="G172" s="16">
+        <v>14110.29</v>
+      </c>
+      <c r="H172" s="17">
+        <v>0.0066296847427</v>
+      </c>
+      <c r="I172" s="16">
+        <v>7.76</v>
       </c>
       <c r="J172" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="173" spans="2:10" ht="15" customHeight="1">
-      <c r="B173" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D173" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F173" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G173" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I173" s="9" t="s">
-        <v>13</v>
+      <c r="B173" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C173" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F173" s="15">
+        <v>94</v>
+      </c>
+      <c r="G173" s="16">
+        <v>9366.16</v>
+      </c>
+      <c r="H173" s="17">
+        <v>0.0044006670344</v>
+      </c>
+      <c r="I173" s="16">
+        <v>7.76</v>
       </c>
       <c r="J173" s="11" t="s">
         <v>13</v>
@@ -6305,36 +6549,57 @@
     </row>
     <row r="174" spans="2:10" ht="15" customHeight="1">
       <c r="B174" s="12" t="s">
-        <v>13</v>
+        <v>248</v>
+      </c>
+      <c r="C174" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D174" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F174" s="15">
+        <v>97</v>
+      </c>
+      <c r="G174" s="16">
+        <v>8654.49</v>
+      </c>
+      <c r="H174" s="17">
+        <v>0.0040662906509</v>
+      </c>
+      <c r="I174" s="16">
+        <v>7.58</v>
       </c>
       <c r="J174" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="175" spans="2:10" ht="15" customHeight="1">
-      <c r="B175" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I175" s="9" t="s">
-        <v>13</v>
+      <c r="B175" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C175" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F175" s="15">
+        <v>135</v>
+      </c>
+      <c r="G175" s="16">
+        <v>8256.23</v>
+      </c>
+      <c r="H175" s="17">
+        <v>0.0038791691781</v>
+      </c>
+      <c r="I175" s="16">
+        <v>7.39</v>
       </c>
       <c r="J175" s="11" t="s">
         <v>13</v>
@@ -6342,36 +6607,57 @@
     </row>
     <row r="176" spans="2:10" ht="15" customHeight="1">
       <c r="B176" s="12" t="s">
-        <v>13</v>
+        <v>248</v>
+      </c>
+      <c r="C176" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D176" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E176" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F176" s="15">
+        <v>109</v>
+      </c>
+      <c r="G176" s="16">
+        <v>7723.66</v>
+      </c>
+      <c r="H176" s="17">
+        <v>0.0036289424852</v>
+      </c>
+      <c r="I176" s="16">
+        <v>7.39</v>
       </c>
       <c r="J176" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="177" spans="2:10" ht="15" customHeight="1">
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C177" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E177" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C177" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G177" s="9">
-        <v>5334.68</v>
-      </c>
-      <c r="H177" s="10">
-        <v>0.0026878033697</v>
-      </c>
-      <c r="I177" s="9" t="s">
-        <v>13</v>
+      <c r="F177" s="15">
+        <v>70</v>
+      </c>
+      <c r="G177" s="16">
+        <v>6420.89</v>
+      </c>
+      <c r="H177" s="17">
+        <v>0.0030168392334</v>
+      </c>
+      <c r="I177" s="16">
+        <v>7.52</v>
       </c>
       <c r="J177" s="11" t="s">
         <v>13</v>
@@ -6379,264 +6665,1056 @@
     </row>
     <row r="178" spans="2:10" ht="15" customHeight="1">
       <c r="B178" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="C178" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E178" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F178" s="15">
+        <v>13</v>
+      </c>
+      <c r="J178" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="2:10" ht="15" customHeight="1">
+      <c r="B179" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="H179" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J179" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10" ht="15" customHeight="1">
+      <c r="B180" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J180" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" ht="15" customHeight="1">
+      <c r="B181" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="H181" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I181" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J181" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" ht="15" customHeight="1">
+      <c r="B182" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J182" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183" spans="2:10" ht="15" customHeight="1">
+      <c r="B183" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="H183" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J183" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="2:10" ht="15" customHeight="1">
+      <c r="B184" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J184" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" spans="2:10" ht="15" customHeight="1">
+      <c r="B185" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D185" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G185" s="9">
+        <v>9398.03</v>
+      </c>
+      <c r="H185" s="10">
+        <v>0.0044156410748</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J185" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186" spans="2:10" ht="15" customHeight="1">
+      <c r="B186" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J186" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10" ht="15" customHeight="1">
+      <c r="B187" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G187" s="9">
+        <v>9398.03</v>
+      </c>
+      <c r="H187" s="10">
+        <v>0.0044156410748</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J187" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188" spans="2:10" ht="15" customHeight="1">
+      <c r="B188" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C188" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E188" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F188" s="15">
+        <v>2000</v>
+      </c>
+      <c r="G188" s="16">
+        <v>9398.03</v>
+      </c>
+      <c r="H188" s="17">
+        <v>0.0044156410748</v>
+      </c>
+      <c r="I188" s="16">
+        <v>6.48</v>
+      </c>
+      <c r="J188" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189" spans="2:10" ht="15" customHeight="1">
+      <c r="B189" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J189" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190" spans="2:10" ht="15" customHeight="1">
+      <c r="B190" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="H190" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J190" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191" spans="2:10" ht="15" customHeight="1">
+      <c r="B191" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J191" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" ht="15" customHeight="1">
+      <c r="B192" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="H192" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J192" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10" ht="15" customHeight="1">
+      <c r="B193" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J193" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10" ht="15" customHeight="1">
+      <c r="B194" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="H194" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J194" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" ht="15" customHeight="1">
+      <c r="B195" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J195" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" ht="15" customHeight="1">
+      <c r="B196" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F196" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G196" s="9">
+        <v>5471.76</v>
+      </c>
+      <c r="H196" s="10">
+        <v>0.0025708928581</v>
+      </c>
+      <c r="I196" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J196" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10" ht="15" customHeight="1">
+      <c r="B197" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C197" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D197" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E197" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="F197" s="15">
         <v>48894.48</v>
       </c>
-      <c r="G178" s="16">
-        <v>5334.68</v>
-      </c>
-      <c r="H178" s="17">
-        <v>0.0026878033697</v>
-      </c>
-      <c r="I178" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J178" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="179" spans="2:10" ht="15" customHeight="1">
-      <c r="B179" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J179" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="180" spans="2:10" ht="15" customHeight="1">
-      <c r="B180" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D180" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E180" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F180" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G180" s="9">
-        <v>8778.67</v>
-      </c>
-      <c r="H180" s="10">
-        <v>0.0044230092166</v>
-      </c>
-      <c r="I180" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J180" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="181" spans="2:10" ht="15" customHeight="1">
-      <c r="B181" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J181" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="182" spans="2:10" ht="15" customHeight="1">
-      <c r="B182" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="C182" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D182" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E182" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F182" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G182" s="20">
-        <v>48460.68459579954</v>
-      </c>
-      <c r="H182" s="21">
-        <v>0.024416233280576717</v>
-      </c>
-      <c r="I182" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J182" s="22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="183" spans="2:10" ht="15" customHeight="1">
-      <c r="B183" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="C183" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D183" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E183" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F183" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G183" s="20">
-        <v>1984773.1645958</v>
-      </c>
-      <c r="H183" s="21">
-        <v>0.9999999999927768</v>
-      </c>
-      <c r="I183" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J183" s="22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="186" spans="2:9" ht="15" customHeight="1">
-      <c r="B186" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C186" s="23"/>
-      <c r="D186" s="23"/>
-      <c r="E186" s="23"/>
-      <c r="F186" s="23"/>
-      <c r="G186" s="23"/>
-      <c r="H186" s="23"/>
-      <c r="I186" s="23"/>
-    </row>
-    <row r="187" spans="2:8" ht="15" customHeight="1">
-      <c r="B187" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C187" s="23"/>
-      <c r="D187" s="23"/>
-      <c r="E187" s="23"/>
-      <c r="F187" s="23"/>
-      <c r="G187" s="23"/>
-      <c r="H187" s="23"/>
-    </row>
-    <row r="188" spans="2:8" ht="15" customHeight="1">
-      <c r="B188" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C188" s="23"/>
-      <c r="D188" s="23"/>
-      <c r="E188" s="23"/>
-      <c r="F188" s="23"/>
-      <c r="G188" s="23"/>
-      <c r="H188" s="23"/>
-    </row>
-    <row r="189" spans="2:8" ht="15" customHeight="1">
-      <c r="B189" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="C189" s="23"/>
-      <c r="D189" s="23"/>
-      <c r="E189" s="23"/>
-      <c r="F189" s="23"/>
-      <c r="G189" s="23"/>
-      <c r="H189" s="23"/>
-    </row>
-    <row r="190" spans="2:8" ht="15" customHeight="1">
-      <c r="B190" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="C190" s="23"/>
-      <c r="D190" s="23"/>
-      <c r="E190" s="23"/>
-      <c r="F190" s="23"/>
-      <c r="G190" s="23"/>
-      <c r="H190" s="23"/>
-    </row>
-    <row r="191" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B191" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C191" s="23"/>
-      <c r="D191" s="23"/>
-      <c r="E191" s="23"/>
-      <c r="F191" s="23"/>
-      <c r="G191" s="23"/>
-      <c r="H191" s="23"/>
-    </row>
-    <row r="192" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B192" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="C192" s="23"/>
-      <c r="D192" s="23"/>
-      <c r="E192" s="23"/>
-      <c r="F192" s="23"/>
-      <c r="G192" s="23"/>
-      <c r="H192" s="23"/>
-    </row>
-    <row r="193" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B193" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="C193" s="23"/>
-      <c r="D193" s="23"/>
-      <c r="E193" s="23"/>
-      <c r="F193" s="23"/>
-      <c r="G193" s="23"/>
-      <c r="H193" s="23"/>
-    </row>
-    <row r="194" spans="2:7" ht="60.75" customHeight="1">
-      <c r="B194" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="C194" s="25"/>
-      <c r="D194" s="25"/>
-      <c r="E194" s="25"/>
-      <c r="F194" s="25"/>
-      <c r="G194" s="25"/>
-    </row>
-    <row r="197" ht="15">
-      <c r="B197" s="23" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="212" ht="15">
-      <c r="B212" s="23" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="213" ht="15">
-      <c r="B213" s="23" t="s">
-        <v>265</v>
+      <c r="G197" s="16">
+        <v>5471.76</v>
+      </c>
+      <c r="H197" s="17">
+        <v>0.0025708928581</v>
+      </c>
+      <c r="I197" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J197" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" ht="15" customHeight="1">
+      <c r="B198" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J198" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" ht="15" customHeight="1">
+      <c r="B199" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G199" s="9">
+        <v>38037.12</v>
+      </c>
+      <c r="H199" s="10">
+        <v>0.0178716464452</v>
+      </c>
+      <c r="I199" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J199" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" ht="15" customHeight="1">
+      <c r="B200" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J200" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" ht="15" customHeight="1">
+      <c r="B201" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C201" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D201" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E201" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F201" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G201" s="20">
+        <v>52066.44207998994</v>
+      </c>
+      <c r="H201" s="21">
+        <v>0.024463288611683388</v>
+      </c>
+      <c r="I201" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J201" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10" ht="15" customHeight="1">
+      <c r="B202" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C202" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D202" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E202" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G202" s="20">
+        <v>2128350.07207999</v>
+      </c>
+      <c r="H202" s="21">
+        <v>0.9999999999912833</v>
+      </c>
+      <c r="I202" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J202" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10" ht="15" customHeight="1">
+      <c r="B203" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C203" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D203" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E203" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F203" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G203" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H203" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I203" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J203" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" ht="15" customHeight="1">
+      <c r="B204" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C204" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D204" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F204" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G204" s="20">
+        <v>-80000</v>
+      </c>
+      <c r="H204" s="21">
+        <v>-0.03758780148503378</v>
+      </c>
+      <c r="I204" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J204" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10" ht="15" customHeight="1">
+      <c r="B205" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G205" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H205" s="17">
+        <v>-0.003523856389221917</v>
+      </c>
+      <c r="I205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J205" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10" ht="15" customHeight="1">
+      <c r="B206" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G206" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H206" s="17">
+        <v>-0.0023492375928146113</v>
+      </c>
+      <c r="I206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J206" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10" ht="15" customHeight="1">
+      <c r="B207" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C207" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D207" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E207" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G207" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H207" s="17">
+        <v>-0.003523856389221917</v>
+      </c>
+      <c r="I207" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J207" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10" ht="15" customHeight="1">
+      <c r="B208" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G208" s="16">
+        <v>-2500</v>
+      </c>
+      <c r="H208" s="17">
+        <v>-0.0011746187964073057</v>
+      </c>
+      <c r="I208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J208" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="2:10" ht="15" customHeight="1">
+      <c r="B209" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G209" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H209" s="17">
+        <v>-0.004698475185629223</v>
+      </c>
+      <c r="I209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J209" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210" spans="2:10" ht="15" customHeight="1">
+      <c r="B210" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G210" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H210" s="17">
+        <v>-0.004698475185629223</v>
+      </c>
+      <c r="I210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J210" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10" ht="15" customHeight="1">
+      <c r="B211" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G211" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H211" s="17">
+        <v>-0.004698475185629223</v>
+      </c>
+      <c r="I211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J211" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212" spans="2:10" ht="15" customHeight="1">
+      <c r="B212" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G212" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H212" s="17">
+        <v>-0.003523856389221917</v>
+      </c>
+      <c r="I212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J212" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" ht="15" customHeight="1">
+      <c r="B213" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G213" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H213" s="17">
+        <v>-0.003523856389221917</v>
+      </c>
+      <c r="I213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J213" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" ht="15" customHeight="1">
+      <c r="B214" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G214" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H214" s="17">
+        <v>-0.0023492375928146113</v>
+      </c>
+      <c r="I214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J214" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" ht="15" customHeight="1">
+      <c r="B215" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C215" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E215" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G215" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H215" s="17">
+        <v>-0.0023492375928146113</v>
+      </c>
+      <c r="I215" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J215" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="2:10" ht="15" customHeight="1">
+      <c r="B216" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C216" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D216" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G216" s="16">
+        <v>-2500</v>
+      </c>
+      <c r="H216" s="17">
+        <v>-0.0011746187964073057</v>
+      </c>
+      <c r="I216" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J216" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" ht="15" customHeight="1">
+      <c r="B217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I217" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J217" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="220" spans="2:9" ht="15" customHeight="1">
+      <c r="B220" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C220" s="24"/>
+      <c r="D220" s="24"/>
+      <c r="E220" s="24"/>
+      <c r="F220" s="24"/>
+      <c r="G220" s="24"/>
+      <c r="H220" s="24"/>
+      <c r="I220" s="24"/>
+    </row>
+    <row r="221" spans="2:8" ht="15" customHeight="1">
+      <c r="B221" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C221" s="24"/>
+      <c r="D221" s="24"/>
+      <c r="E221" s="24"/>
+      <c r="F221" s="24"/>
+      <c r="G221" s="24"/>
+      <c r="H221" s="24"/>
+    </row>
+    <row r="222" spans="2:8" ht="15" customHeight="1">
+      <c r="B222" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="C222" s="24"/>
+      <c r="D222" s="24"/>
+      <c r="E222" s="24"/>
+      <c r="F222" s="24"/>
+      <c r="G222" s="24"/>
+      <c r="H222" s="24"/>
+    </row>
+    <row r="223" spans="2:8" ht="15" customHeight="1">
+      <c r="B223" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="C223" s="24"/>
+      <c r="D223" s="24"/>
+      <c r="E223" s="24"/>
+      <c r="F223" s="24"/>
+      <c r="G223" s="24"/>
+      <c r="H223" s="24"/>
+    </row>
+    <row r="224" spans="2:8" ht="15" customHeight="1">
+      <c r="B224" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C224" s="24"/>
+      <c r="D224" s="24"/>
+      <c r="E224" s="24"/>
+      <c r="F224" s="24"/>
+      <c r="G224" s="24"/>
+      <c r="H224" s="24"/>
+    </row>
+    <row r="225" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B225" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="C225" s="24"/>
+      <c r="D225" s="24"/>
+      <c r="E225" s="24"/>
+      <c r="F225" s="24"/>
+      <c r="G225" s="24"/>
+      <c r="H225" s="24"/>
+    </row>
+    <row r="226" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B226" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="C226" s="24"/>
+      <c r="D226" s="24"/>
+      <c r="E226" s="24"/>
+      <c r="F226" s="24"/>
+      <c r="G226" s="24"/>
+      <c r="H226" s="24"/>
+    </row>
+    <row r="227" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B227" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="C227" s="24"/>
+      <c r="D227" s="24"/>
+      <c r="E227" s="24"/>
+      <c r="F227" s="24"/>
+      <c r="G227" s="24"/>
+      <c r="H227" s="24"/>
+    </row>
+    <row r="228" spans="2:7" ht="47.25" customHeight="1">
+      <c r="B228" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C228" s="26"/>
+      <c r="D228" s="26"/>
+      <c r="E228" s="26"/>
+      <c r="F228" s="26"/>
+      <c r="G228" s="26"/>
+    </row>
+    <row r="231" ht="15">
+      <c r="B231" s="24" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="246" ht="15">
+      <c r="B246" s="24" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B193:H193"/>
-    <mergeCell ref="B194:G194"/>
-    <mergeCell ref="B188:H188"/>
-    <mergeCell ref="B189:H189"/>
-    <mergeCell ref="B190:H190"/>
-    <mergeCell ref="B191:H191"/>
-    <mergeCell ref="B192:H192"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B186:I186"/>
-    <mergeCell ref="B187:H187"/>
+    <mergeCell ref="B220:I220"/>
+    <mergeCell ref="B221:H221"/>
+    <mergeCell ref="B227:H227"/>
+    <mergeCell ref="B228:G228"/>
+    <mergeCell ref="B222:H222"/>
+    <mergeCell ref="B223:H223"/>
+    <mergeCell ref="B224:H224"/>
+    <mergeCell ref="B225:H225"/>
+    <mergeCell ref="B226:H226"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
